--- a/BISTTemelVeriler.xlsx
+++ b/BISTTemelVeriler.xlsx
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
         <v>203.3863</v>
@@ -1505,13 +1505,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.4</v>
       </c>
       <c r="P11" t="n">
         <v>26.96</v>
@@ -2074,19 +2071,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12.5</v>
+        <v>18.7</v>
       </c>
       <c r="D17" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
         <v>167.4</v>
@@ -2559,13 +2556,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O22" t="n">
-        <v>37.2</v>
+        <v>36.7</v>
       </c>
       <c r="P22" t="n">
         <v>7</v>
@@ -4626,10 +4623,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="P44" t="n">
         <v>101.7159</v>
@@ -4702,10 +4699,10 @@
         <v>2.6</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="O45" t="n">
-        <v>39.4</v>
+        <v>36.3</v>
       </c>
       <c r="P45" t="n">
         <v>23.9669</v>
@@ -4883,14 +4880,17 @@
           <t>Arçelik Hisse Senedi</t>
         </is>
       </c>
+      <c r="C47" t="n">
+        <v>13.4</v>
+      </c>
       <c r="D47" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O47" t="n">
         <v>0.4</v>
@@ -4920,13 +4920,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>70390.60000000001</v>
+        <v>73314.5</v>
       </c>
       <c r="W47" t="n">
         <v>675.7</v>
       </c>
       <c r="X47" t="n">
-        <v>-8355.700000000001</v>
+        <v>-1816.8</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -7703,17 +7703,8 @@
           <t>Aygaz Hisse Senedi</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="D75" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F75" t="n">
-        <v>0.5</v>
+        <v>35.9</v>
       </c>
       <c r="O75" t="n">
         <v>0.5</v>
@@ -9943,16 +9934,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="D97" t="n">
         <v>6.5</v>
       </c>
       <c r="E97" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O97" t="n">
         <v>0.5</v>
@@ -13427,16 +13418,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="D131" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="E131" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O131" t="n">
         <v>1</v>
@@ -14139,19 +14130,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="D138" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="E138" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F138" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O138" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="P138" t="n">
         <v>46.4037</v>
@@ -15220,13 +15211,13 @@
         </is>
       </c>
       <c r="V148" t="n">
-        <v>13949.8</v>
+        <v>16106.3</v>
       </c>
       <c r="W148" t="n">
         <v>1078.3</v>
       </c>
       <c r="X148" t="n">
-        <v>2215.1</v>
+        <v>737.7</v>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
@@ -17151,7 +17142,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="D168" t="n">
         <v>3.6</v>
@@ -20911,19 +20902,19 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>10.2</v>
+        <v>8</v>
       </c>
       <c r="D205" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="E205" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="O205" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O205" t="n">
-        <v>2</v>
       </c>
       <c r="P205" t="n">
         <v>82.1562</v>
@@ -23779,10 +23770,10 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D233" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="E233" t="n">
         <v>1.9</v>
@@ -35184,19 +35175,19 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>10.3</v>
+        <v>12.1</v>
       </c>
       <c r="D346" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E346" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O346" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="P346" t="n">
         <v>14.14</v>
@@ -37209,16 +37200,16 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="D366" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="E366" t="n">
         <v>1.4</v>
       </c>
       <c r="F366" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O366" t="n">
         <v>1.1</v>
@@ -37621,19 +37612,19 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D370" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="E370" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="F370" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="O370" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="P370" t="n">
         <v>131.8</v>
@@ -39156,13 +39147,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D386" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="E386" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F386" t="n">
         <v>0.5</v>
@@ -40397,13 +40388,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>7.8</v>
+        <v>3.1</v>
       </c>
       <c r="D398" t="n">
         <v>2.5</v>
       </c>
       <c r="E398" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F398" t="n">
         <v>0.2</v>
@@ -41296,16 +41287,19 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>12.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D407" t="n">
-        <v>5</v>
+        <v>4.2</v>
+      </c>
+      <c r="E407" t="n">
+        <v>5.5</v>
       </c>
       <c r="F407" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O407" t="n">
         <v>1.3</v>
-      </c>
-      <c r="O407" t="n">
-        <v>1.4</v>
       </c>
       <c r="P407" t="n">
         <v>408</v>
@@ -44297,13 +44291,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="D436" t="n">
         <v>5.9</v>
       </c>
       <c r="E436" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F436" t="n">
         <v>1.6</v>
@@ -46452,17 +46446,8 @@
           <t>Petkim Hisse Senedi</t>
         </is>
       </c>
-      <c r="D457" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E457" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F457" t="n">
+      <c r="O457" t="n">
         <v>0.8</v>
-      </c>
-      <c r="O457" t="n">
-        <v>0.9</v>
       </c>
       <c r="P457" t="n">
         <v>17.29</v>
@@ -46644,7 +46629,7 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="D459" t="n">
         <v>3.9</v>
@@ -52870,13 +52855,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>17.6</v>
+        <v>3.9</v>
       </c>
       <c r="D520" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="E520" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F520" t="n">
         <v>0.1</v>
@@ -54082,19 +54067,19 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>12.1</v>
+        <v>18.2</v>
       </c>
       <c r="D532" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="E532" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F532" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O532" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="P532" t="n">
         <v>286</v>
@@ -54276,10 +54261,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="D534" t="n">
         <v>2.1</v>
+      </c>
+      <c r="E534" t="n">
+        <v>1</v>
       </c>
       <c r="F534" t="n">
         <v>0.9</v>
@@ -55097,19 +55085,19 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="D542" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="E542" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F542" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O542" t="n">
         <v>0.6</v>
-      </c>
-      <c r="O542" t="n">
-        <v>0.8</v>
       </c>
       <c r="P542" t="n">
         <v>276.75</v>
@@ -55769,13 +55757,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="D549" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="E549" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F549" t="n">
         <v>0.3</v>
@@ -56824,19 +56812,19 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="D560" t="n">
         <v>1.9</v>
       </c>
       <c r="E560" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F560" t="n">
         <v>0.8</v>
       </c>
       <c r="O560" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P560" t="n">
         <v>57.2</v>
@@ -56909,13 +56897,13 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D561" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E561" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F561" t="n">
         <v>0.6</v>
@@ -57509,7 +57497,7 @@
         <v>4.2</v>
       </c>
       <c r="E567" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="P567" t="n">
         <v>11.51</v>
@@ -57885,10 +57873,10 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D571" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E571" t="n">
         <v>0.9</v>
@@ -58221,13 +58209,13 @@
         </is>
       </c>
       <c r="V574" t="n">
-        <v>12913.5</v>
+        <v>13712</v>
       </c>
       <c r="W574" t="n">
         <v>750</v>
       </c>
       <c r="X574" t="n">
-        <v>-287.2</v>
+        <v>-130.9</v>
       </c>
       <c r="Y574" t="inlineStr">
         <is>

--- a/BISTTemelVeriler.xlsx
+++ b/BISTTemelVeriler.xlsx
@@ -631,7 +631,7 @@
         <v>0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="H2" t="n">
         <v>8424</v>
@@ -740,7 +740,7 @@
         <v>5.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="H3" t="n">
         <v>2087.8</v>
@@ -832,20 +832,23 @@
           <t>Acıselsan Acıpayam Selüloz Hisse Senedi</t>
         </is>
       </c>
+      <c r="D4" t="n">
+        <v>17.9</v>
+      </c>
       <c r="E4" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
         <v>1294.1</v>
       </c>
       <c r="I4" t="n">
-        <v>168.2</v>
+        <v>146.6</v>
       </c>
       <c r="J4" t="n">
         <v>48.3</v>
@@ -890,13 +893,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>575</v>
+        <v>638.6</v>
       </c>
       <c r="W4" t="n">
         <v>10.7</v>
       </c>
       <c r="X4" t="n">
-        <v>-67.2</v>
+        <v>5.8</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -936,19 +939,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="H5" t="n">
         <v>12520.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1288.7</v>
+        <v>1625.7</v>
       </c>
       <c r="J5" t="n">
         <v>27.6</v>
@@ -1045,7 +1048,7 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>14.99</v>
+        <v>14.37</v>
       </c>
       <c r="H6" t="n">
         <v>5443.2</v>
@@ -1145,7 +1148,7 @@
         <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H7" t="n">
         <v>32587.5</v>
@@ -1175,10 +1178,10 @@
         <v>50.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>66.95</v>
+        <v>65.05</v>
       </c>
       <c r="R7" t="n">
-        <v>16.9</v>
+        <v>15</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1332,7 +1335,7 @@
         <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
         <v>5412</v>
@@ -1587,7 +1590,7 @@
         <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.18</v>
+        <v>3.78</v>
       </c>
       <c r="H12" t="n">
         <v>7368</v>
@@ -1683,7 +1686,7 @@
         <v>0.4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H13" t="n">
         <v>2530.7</v>
@@ -1792,7 +1795,7 @@
         <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>12.01</v>
+        <v>11.99</v>
       </c>
       <c r="H14" t="n">
         <v>71448</v>
@@ -1895,7 +1898,7 @@
         <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.41</v>
+        <v>10.24</v>
       </c>
       <c r="H15" t="n">
         <v>13275.6</v>
@@ -2165,7 +2168,7 @@
         <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="H18" t="n">
         <v>7452.1</v>
@@ -2268,7 +2271,7 @@
         <v>0.3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.27</v>
+        <v>6.26</v>
       </c>
       <c r="H19" t="n">
         <v>11115</v>
@@ -2374,7 +2377,7 @@
         <v>5.7</v>
       </c>
       <c r="G20" t="n">
-        <v>6.63</v>
+        <v>6.79</v>
       </c>
       <c r="H20" t="n">
         <v>35266.8</v>
@@ -2641,7 +2644,7 @@
         <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66</v>
+        <v>3.36</v>
       </c>
       <c r="H23" t="n">
         <v>7823.3</v>
@@ -2741,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H24" t="n">
         <v>9670</v>
@@ -2850,7 +2853,7 @@
         <v>1.9</v>
       </c>
       <c r="G25" t="n">
-        <v>17.75</v>
+        <v>17.37</v>
       </c>
       <c r="H25" t="n">
         <v>41142.2</v>
@@ -3111,19 +3114,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="F28" t="n">
-        <v>31.4</v>
+        <v>29.8</v>
       </c>
       <c r="G28" t="n">
-        <v>6.9</v>
+        <v>6.59</v>
       </c>
       <c r="H28" t="n">
         <v>2290.2</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>83.40000000000001</v>
@@ -3217,7 +3220,7 @@
         <v>1.1</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H29" t="n">
         <v>682.5</v>
@@ -3317,13 +3320,13 @@
         <v>0.5</v>
       </c>
       <c r="P30" t="n">
-        <v>86.95</v>
+        <v>84.0547</v>
       </c>
       <c r="Q30" t="n">
-        <v>115.8</v>
+        <v>111.944</v>
       </c>
       <c r="R30" t="n">
-        <v>28.85</v>
+        <v>27.8893</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3469,7 +3472,7 @@
         <v>1.2</v>
       </c>
       <c r="G32" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H32" t="n">
         <v>8380.799999999999</v>
@@ -3566,7 +3569,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="E33" t="n">
         <v>1.6</v>
@@ -3575,13 +3578,13 @@
         <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>15.39</v>
+        <v>14.89</v>
       </c>
       <c r="H33" t="n">
         <v>5313.6</v>
       </c>
       <c r="I33" t="n">
-        <v>-1567.2</v>
+        <v>-1225.3</v>
       </c>
       <c r="J33" t="n">
         <v>35</v>
@@ -3681,7 +3684,7 @@
         <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>7.69</v>
+        <v>7.55</v>
       </c>
       <c r="H34" t="n">
         <v>15169</v>
@@ -3781,7 +3784,7 @@
         <v>0.8</v>
       </c>
       <c r="G35" t="n">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="H35" t="n">
         <v>12841</v>
@@ -3878,19 +3881,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="F36" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G36" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H36" t="n">
         <v>8261.4</v>
       </c>
       <c r="I36" t="n">
-        <v>226.5</v>
+        <v>199.2</v>
       </c>
       <c r="J36" t="n">
         <v>18.9</v>
@@ -3990,7 +3993,7 @@
         <v>1.2</v>
       </c>
       <c r="G37" t="n">
-        <v>6.28</v>
+        <v>6.26</v>
       </c>
       <c r="H37" t="n">
         <v>6018</v>
@@ -4093,7 +4096,7 @@
         <v>8.4</v>
       </c>
       <c r="G38" t="n">
-        <v>15.99</v>
+        <v>16</v>
       </c>
       <c r="H38" t="n">
         <v>40096</v>
@@ -4211,7 +4214,7 @@
         <v>5.6</v>
       </c>
       <c r="G40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="H40" t="n">
         <v>16010</v>
@@ -4317,7 +4320,7 @@
         <v>0.9</v>
       </c>
       <c r="G41" t="n">
-        <v>7.77</v>
+        <v>8.35</v>
       </c>
       <c r="H41" t="n">
         <v>5216</v>
@@ -4420,7 +4423,7 @@
         <v>1.8</v>
       </c>
       <c r="G42" t="n">
-        <v>18.19</v>
+        <v>18.11</v>
       </c>
       <c r="H42" t="n">
         <v>12746.5</v>
@@ -4517,22 +4520,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>21.4</v>
+        <v>32.9</v>
       </c>
       <c r="E43" t="n">
         <v>1.4</v>
       </c>
       <c r="F43" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G43" t="n">
-        <v>9.359999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H43" t="n">
         <v>2457.4</v>
       </c>
       <c r="I43" t="n">
-        <v>193.1</v>
+        <v>361.9</v>
       </c>
       <c r="J43" t="n">
         <v>35.4</v>
@@ -4784,7 +4787,7 @@
         <v>0.9</v>
       </c>
       <c r="G46" t="n">
-        <v>14.18</v>
+        <v>14.67</v>
       </c>
       <c r="H46" t="n">
         <v>26125</v>
@@ -4978,7 +4981,7 @@
         <v>4.2</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="H48" t="n">
         <v>16178.2</v>
@@ -5084,7 +5087,7 @@
         <v>0.2</v>
       </c>
       <c r="G49" t="n">
-        <v>26.75</v>
+        <v>24.7</v>
       </c>
       <c r="H49" t="n">
         <v>3850</v>
@@ -5187,7 +5190,7 @@
         <v>11.6</v>
       </c>
       <c r="G50" t="n">
-        <v>10.8</v>
+        <v>11.88</v>
       </c>
       <c r="H50" t="n">
         <v>5964.2</v>
@@ -5290,7 +5293,7 @@
         <v>3.3</v>
       </c>
       <c r="G51" t="n">
-        <v>15.25</v>
+        <v>15.21</v>
       </c>
       <c r="H51" t="n">
         <v>34792.7</v>
@@ -5393,7 +5396,7 @@
         <v>32.9</v>
       </c>
       <c r="G52" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="H52" t="n">
         <v>6131.8</v>
@@ -5490,25 +5493,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12.5</v>
+        <v>16.4</v>
       </c>
       <c r="D53" t="n">
-        <v>15.8</v>
+        <v>16.3</v>
       </c>
       <c r="E53" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F53" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="G53" t="n">
-        <v>5.58</v>
+        <v>5.13</v>
       </c>
       <c r="H53" t="n">
         <v>3040.8</v>
       </c>
       <c r="I53" t="n">
-        <v>217.9</v>
+        <v>326.7</v>
       </c>
       <c r="J53" t="n">
         <v>28.3</v>
@@ -5553,13 +5556,13 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>2196.5</v>
+        <v>2429.5</v>
       </c>
       <c r="W53" t="n">
         <v>70</v>
       </c>
       <c r="X53" t="n">
-        <v>243.6</v>
+        <v>13.9</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5602,7 +5605,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" t="n">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="H54" t="n">
         <v>1608</v>
@@ -5790,7 +5793,7 @@
         <v>0.3</v>
       </c>
       <c r="G56" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="H56" t="n">
         <v>8211.1</v>
@@ -6011,13 +6014,13 @@
         <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>60</v>
+        <v>60.25</v>
       </c>
       <c r="Q58" t="n">
         <v>71.2</v>
       </c>
       <c r="R58" t="n">
-        <v>11.2</v>
+        <v>10.95</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6084,7 +6087,7 @@
         <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="H59" t="n">
         <v>625.1</v>
@@ -6278,7 +6281,7 @@
         <v>2.4</v>
       </c>
       <c r="G61" t="n">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
       <c r="H61" t="n">
         <v>14025</v>
@@ -6387,7 +6390,7 @@
         <v>4.3</v>
       </c>
       <c r="G62" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H62" t="n">
         <v>11561</v>
@@ -6513,13 +6516,13 @@
         <v>-3.87</v>
       </c>
       <c r="P63" t="n">
-        <v>76.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Q63" t="n">
         <v>122.2</v>
       </c>
       <c r="R63" t="n">
-        <v>46</v>
+        <v>40.3</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6582,23 +6585,20 @@
           <t>Atlas YO Hisse Senedi</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>0.3</v>
+      <c r="C64" t="n">
+        <v>5.9</v>
       </c>
       <c r="E64" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G64" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="H64" t="n">
         <v>486.6</v>
       </c>
       <c r="I64" t="n">
-        <v>-453</v>
+        <v>-577.5</v>
       </c>
       <c r="J64" t="n">
         <v>99.2</v>
@@ -6792,7 +6792,7 @@
         <v>0.7</v>
       </c>
       <c r="G66" t="n">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="H66" t="n">
         <v>1424</v>
@@ -6895,7 +6895,7 @@
         <v>1.3</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
       <c r="H67" t="n">
         <v>1452</v>
@@ -7001,7 +7001,7 @@
         <v>1.1</v>
       </c>
       <c r="G68" t="n">
-        <v>1.47</v>
+        <v>0.92</v>
       </c>
       <c r="H68" t="n">
         <v>1223.1</v>
@@ -7031,10 +7031,10 @@
         <v>4.07</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="R68" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -7098,19 +7098,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G69" t="n">
-        <v>4.54</v>
+        <v>4.59</v>
       </c>
       <c r="H69" t="n">
         <v>23900</v>
       </c>
       <c r="I69" t="n">
-        <v>-775.3</v>
+        <v>-1595.9</v>
       </c>
       <c r="J69" t="n">
         <v>21.7</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>40223.6</v>
+        <v>44419.7</v>
       </c>
       <c r="W69" t="n">
         <v>400</v>
       </c>
       <c r="X69" t="n">
-        <v>1609</v>
+        <v>157.6</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>24.8</v>
       </c>
       <c r="G70" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="H70" t="n">
         <v>862.6</v>
@@ -7310,7 +7310,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>0.09</v>
+        <v>0.51</v>
       </c>
       <c r="H71" t="n">
         <v>26325</v>
@@ -7337,13 +7337,13 @@
         <v>-10.82</v>
       </c>
       <c r="P71" t="n">
-        <v>480</v>
+        <v>486.5</v>
       </c>
       <c r="Q71" t="n">
         <v>1305</v>
       </c>
       <c r="R71" t="n">
-        <v>825</v>
+        <v>818.5</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>2.1</v>
       </c>
       <c r="G73" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="H73" t="n">
         <v>9995.5</v>
@@ -7631,13 +7631,13 @@
         <v>2.06</v>
       </c>
       <c r="P74" t="n">
-        <v>18.5</v>
+        <v>19.8</v>
       </c>
       <c r="Q74" t="n">
         <v>33.04</v>
       </c>
       <c r="R74" t="n">
-        <v>14.54</v>
+        <v>13.24</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0.6</v>
       </c>
       <c r="P75" t="n">
-        <v>213.0006</v>
+        <v>216.2395</v>
       </c>
       <c r="Q75" t="n">
         <v>291</v>
       </c>
       <c r="R75" t="n">
-        <v>77.99939999999999</v>
+        <v>74.76049999999999</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>0.7</v>
       </c>
       <c r="G76" t="n">
-        <v>2.18</v>
+        <v>1.48</v>
       </c>
       <c r="H76" t="n">
         <v>4470</v>
@@ -7816,10 +7816,10 @@
         <v>3.81</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
       <c r="R76" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>2.1</v>
       </c>
       <c r="G77" t="n">
-        <v>4.98</v>
+        <v>4.67</v>
       </c>
       <c r="H77" t="n">
         <v>4563</v>
@@ -7998,7 +7998,7 @@
         <v>6.6</v>
       </c>
       <c r="G78" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="H78" t="n">
         <v>6600</v>
@@ -8025,13 +8025,13 @@
         <v>-3.72</v>
       </c>
       <c r="P78" t="n">
-        <v>98.5</v>
+        <v>109.1</v>
       </c>
       <c r="Q78" t="n">
         <v>145.8</v>
       </c>
       <c r="R78" t="n">
-        <v>47.3</v>
+        <v>36.7</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>0.7</v>
       </c>
       <c r="G79" t="n">
-        <v>6.49</v>
+        <v>6.56</v>
       </c>
       <c r="H79" t="n">
         <v>3096</v>
@@ -8359,19 +8359,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F82" t="n">
         <v>0.4</v>
       </c>
       <c r="G82" t="n">
-        <v>77.84999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="H82" t="n">
         <v>16013.8</v>
       </c>
       <c r="I82" t="n">
-        <v>-2450.1</v>
+        <v>-1262.6</v>
       </c>
       <c r="J82" t="n">
         <v>8.300000000000001</v>
@@ -8468,7 +8468,7 @@
         <v>6.7</v>
       </c>
       <c r="G83" t="n">
-        <v>12.96</v>
+        <v>13.13</v>
       </c>
       <c r="H83" t="n">
         <v>15802.5</v>
@@ -8671,25 +8671,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="D85" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G85" t="n">
-        <v>8.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H85" t="n">
         <v>35770</v>
       </c>
       <c r="I85" t="n">
-        <v>-1474.6</v>
+        <v>-4762.7</v>
       </c>
       <c r="J85" t="n">
         <v>15.3</v>
@@ -8780,19 +8780,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="F86" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="G86" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H86" t="n">
         <v>1230</v>
       </c>
       <c r="I86" t="n">
-        <v>199.1</v>
+        <v>182.4</v>
       </c>
       <c r="J86" t="n">
         <v>75.8</v>
@@ -8886,7 +8886,7 @@
         <v>0.6</v>
       </c>
       <c r="G87" t="n">
-        <v>3.02</v>
+        <v>2.26</v>
       </c>
       <c r="H87" t="n">
         <v>3520.8</v>
@@ -8986,7 +8986,7 @@
         <v>0.4</v>
       </c>
       <c r="G88" t="n">
-        <v>10.76</v>
+        <v>10.63</v>
       </c>
       <c r="H88" t="n">
         <v>11648.6</v>
@@ -9095,7 +9095,7 @@
         <v>0.5</v>
       </c>
       <c r="G89" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H89" t="n">
         <v>9943.200000000001</v>
@@ -9204,7 +9204,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="H90" t="n">
         <v>5111.6</v>
@@ -9297,14 +9297,11 @@
           <t>Beyaz Filo Hisse Senedi</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>26.1</v>
-      </c>
       <c r="D91" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="E91" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F91" t="n">
         <v>0.1</v>
@@ -9316,7 +9313,7 @@
         <v>3455.2</v>
       </c>
       <c r="I91" t="n">
-        <v>-791.4</v>
+        <v>-339.2</v>
       </c>
       <c r="J91" t="n">
         <v>24.5</v>
@@ -9413,7 +9410,7 @@
         <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>25.54</v>
+        <v>25.58</v>
       </c>
       <c r="H92" t="n">
         <v>17802.6</v>
@@ -9519,7 +9516,7 @@
         <v>1.1</v>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="H93" t="n">
         <v>8844.5</v>
@@ -9625,7 +9622,7 @@
         <v>0.9</v>
       </c>
       <c r="G94" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="H94" t="n">
         <v>4023.2</v>
@@ -9731,7 +9728,7 @@
         <v>9.1</v>
       </c>
       <c r="G95" t="n">
-        <v>17.32</v>
+        <v>16.38</v>
       </c>
       <c r="H95" t="n">
         <v>10766.8</v>
@@ -9834,7 +9831,7 @@
         <v>12.4</v>
       </c>
       <c r="G96" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H96" t="n">
         <v>7201.9</v>
@@ -10016,19 +10013,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="F98" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="G98" t="n">
-        <v>55.74</v>
+        <v>55.76</v>
       </c>
       <c r="H98" t="n">
         <v>19521.6</v>
       </c>
       <c r="I98" t="n">
-        <v>-296.4</v>
+        <v>-198.4</v>
       </c>
       <c r="J98" t="n">
         <v>15.2</v>
@@ -10073,13 +10070,13 @@
         </is>
       </c>
       <c r="V98" t="n">
-        <v>1884.7</v>
+        <v>1784.9</v>
       </c>
       <c r="W98" t="n">
         <v>112</v>
       </c>
       <c r="X98" t="n">
-        <v>-400.3</v>
+        <v>-293.1</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -10114,20 +10111,17 @@
           <t>1000 Yatırımlar Hisse Senedi</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>8.9</v>
-      </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G99" t="n">
-        <v>4.26</v>
+        <v>5.2</v>
       </c>
       <c r="H99" t="n">
         <v>12991.8</v>
       </c>
       <c r="I99" t="n">
-        <v>-329.5</v>
+        <v>-437.4</v>
       </c>
       <c r="J99" t="n">
         <v>37.9</v>
@@ -10172,13 +10166,13 @@
         </is>
       </c>
       <c r="V99" t="n">
-        <v>13530.2</v>
+        <v>13770.4</v>
       </c>
       <c r="W99" t="n">
         <v>1290.2</v>
       </c>
       <c r="X99" t="n">
-        <v>1461.7</v>
+        <v>-1119.6</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -10220,7 +10214,7 @@
         <v>5.2</v>
       </c>
       <c r="G100" t="n">
-        <v>7.79</v>
+        <v>7.74</v>
       </c>
       <c r="H100" t="n">
         <v>10050</v>
@@ -10405,7 +10399,7 @@
         <v>1.9</v>
       </c>
       <c r="G102" t="n">
-        <v>6.44</v>
+        <v>6.31</v>
       </c>
       <c r="H102" t="n">
         <v>7245.2</v>
@@ -10511,7 +10505,7 @@
         <v>3.1</v>
       </c>
       <c r="G103" t="n">
-        <v>4.32</v>
+        <v>4.51</v>
       </c>
       <c r="H103" t="n">
         <v>3256</v>
@@ -10614,7 +10608,7 @@
         <v>30.7</v>
       </c>
       <c r="G104" t="n">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="H104" t="n">
         <v>6988.4</v>
@@ -10717,7 +10711,7 @@
         <v>0.9</v>
       </c>
       <c r="G105" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="H105" t="n">
         <v>1813</v>
@@ -10747,10 +10741,10 @@
         <v>15.89</v>
       </c>
       <c r="Q105" t="n">
-        <v>19.29</v>
+        <v>19.03</v>
       </c>
       <c r="R105" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10820,7 +10814,7 @@
         <v>5.6</v>
       </c>
       <c r="G106" t="n">
-        <v>9.6</v>
+        <v>9.92</v>
       </c>
       <c r="H106" t="n">
         <v>13575</v>
@@ -10929,7 +10923,7 @@
         <v>0.7</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="H107" t="n">
         <v>1627.8</v>
@@ -11035,7 +11029,7 @@
         <v>0.7</v>
       </c>
       <c r="G108" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H108" t="n">
         <v>7565.8</v>
@@ -11134,7 +11128,7 @@
         <v>2.3</v>
       </c>
       <c r="G109" t="n">
-        <v>5.23</v>
+        <v>6.49</v>
       </c>
       <c r="H109" t="n">
         <v>5334</v>
@@ -11236,7 +11230,7 @@
         <v>1.3</v>
       </c>
       <c r="G110" t="n">
-        <v>12.9</v>
+        <v>13.01</v>
       </c>
       <c r="H110" t="n">
         <v>6873.6</v>
@@ -11333,25 +11327,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>29.9</v>
+        <v>28.5</v>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F111" t="n">
         <v>1.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H111" t="n">
         <v>8515</v>
       </c>
       <c r="I111" t="n">
-        <v>1988.9</v>
+        <v>1804.2</v>
       </c>
       <c r="J111" t="n">
         <v>12.2</v>
@@ -11396,13 +11390,13 @@
         </is>
       </c>
       <c r="V111" t="n">
-        <v>10699.2</v>
+        <v>11763.5</v>
       </c>
       <c r="W111" t="n">
         <v>1300</v>
       </c>
       <c r="X111" t="n">
-        <v>285</v>
+        <v>13.3</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -11451,7 +11445,7 @@
         <v>0.8</v>
       </c>
       <c r="G112" t="n">
-        <v>9.32</v>
+        <v>9.18</v>
       </c>
       <c r="H112" t="n">
         <v>25782.4</v>
@@ -11663,7 +11657,7 @@
         <v>0.9</v>
       </c>
       <c r="G114" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="H114" t="n">
         <v>834</v>
@@ -11690,13 +11684,13 @@
         <v>0.67</v>
       </c>
       <c r="P114" t="n">
-        <v>8.300000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="Q114" t="n">
         <v>9.369999999999999</v>
       </c>
       <c r="R114" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11756,19 +11750,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>17.2</v>
+        <v>16.1</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="F115" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G115" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="H115" t="n">
         <v>5401.2</v>
@@ -11795,10 +11789,10 @@
         <v>82.65000000000001</v>
       </c>
       <c r="Q115" t="n">
-        <v>123.1</v>
+        <v>117</v>
       </c>
       <c r="R115" t="n">
-        <v>40.45</v>
+        <v>34.35</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11862,7 +11856,7 @@
         <v>0.9</v>
       </c>
       <c r="G116" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="H116" t="n">
         <v>3346.6</v>
@@ -12068,7 +12062,7 @@
         <v>1.2</v>
       </c>
       <c r="G118" t="n">
-        <v>9.279999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H118" t="n">
         <v>77549.10000000001</v>
@@ -12171,7 +12165,7 @@
         <v>1.7</v>
       </c>
       <c r="G119" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="H119" t="n">
         <v>59175</v>
@@ -12380,7 +12374,7 @@
         <v>2.8</v>
       </c>
       <c r="G121" t="n">
-        <v>9.92</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H121" t="n">
         <v>34707.6</v>
@@ -12486,7 +12480,7 @@
         <v>1.1</v>
       </c>
       <c r="G122" t="n">
-        <v>3.97</v>
+        <v>3.9</v>
       </c>
       <c r="H122" t="n">
         <v>9195</v>
@@ -12583,25 +12577,25 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="D123" t="n">
-        <v>19.5</v>
+        <v>15.6</v>
       </c>
       <c r="E123" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F123" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="G123" t="n">
-        <v>7.26</v>
+        <v>8.15</v>
       </c>
       <c r="H123" t="n">
         <v>11931.4</v>
       </c>
       <c r="I123" t="n">
-        <v>-1184</v>
+        <v>-1091.3</v>
       </c>
       <c r="J123" t="n">
         <v>27</v>
@@ -12646,13 +12640,13 @@
         </is>
       </c>
       <c r="V123" t="n">
-        <v>7484.1</v>
+        <v>8057.3</v>
       </c>
       <c r="W123" t="n">
         <v>268</v>
       </c>
       <c r="X123" t="n">
-        <v>1635.5</v>
+        <v>-178.5</v>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
@@ -12698,7 +12692,7 @@
         <v>7.4</v>
       </c>
       <c r="G124" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H124" t="n">
         <v>4869.1</v>
@@ -12801,7 +12795,7 @@
         <v>9515.200000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>-8.1</v>
+        <v>5</v>
       </c>
       <c r="J125" t="n">
         <v>45.5</v>
@@ -12822,13 +12816,13 @@
         <v>8.93</v>
       </c>
       <c r="P125" t="n">
-        <v>633</v>
+        <v>652.5</v>
       </c>
       <c r="Q125" t="n">
         <v>1295</v>
       </c>
       <c r="R125" t="n">
-        <v>662</v>
+        <v>642.5</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -12904,7 +12898,7 @@
         <v>1.6</v>
       </c>
       <c r="G126" t="n">
-        <v>1.42</v>
+        <v>0.64</v>
       </c>
       <c r="H126" t="n">
         <v>4459.4</v>
@@ -13006,7 +13000,7 @@
         <v>1.1</v>
       </c>
       <c r="G127" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="H127" t="n">
         <v>3452.4</v>
@@ -13112,7 +13106,7 @@
         <v>2.9</v>
       </c>
       <c r="G128" t="n">
-        <v>8.68</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H128" t="n">
         <v>17900</v>
@@ -13142,10 +13136,10 @@
         <v>1.47</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R128" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -13242,10 +13236,10 @@
         <v>88</v>
       </c>
       <c r="Q129" t="n">
-        <v>105.6</v>
+        <v>104.9</v>
       </c>
       <c r="R129" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -13309,25 +13303,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="D130" t="n">
-        <v>8.199999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="E130" t="n">
         <v>0.6</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G130" t="n">
-        <v>6.35</v>
+        <v>4.92</v>
       </c>
       <c r="H130" t="n">
         <v>7334.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-1105.9</v>
+        <v>-896.8</v>
       </c>
       <c r="J130" t="n">
         <v>20</v>
@@ -13372,13 +13366,13 @@
         </is>
       </c>
       <c r="V130" t="n">
-        <v>12759.4</v>
+        <v>13276.7</v>
       </c>
       <c r="W130" t="n">
         <v>165.2</v>
       </c>
       <c r="X130" t="n">
-        <v>1787.9</v>
+        <v>-782.7</v>
       </c>
       <c r="Y130" t="inlineStr">
         <is>
@@ -13509,7 +13503,7 @@
         <v>2.5</v>
       </c>
       <c r="G132" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="H132" t="n">
         <v>5080.9</v>
@@ -13606,19 +13600,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
         <v>2.6</v>
       </c>
       <c r="G133" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="H133" t="n">
         <v>3788.9</v>
       </c>
       <c r="I133" t="n">
-        <v>669.1</v>
+        <v>639.8</v>
       </c>
       <c r="J133" t="n">
         <v>97.3</v>
@@ -13718,13 +13712,13 @@
         <v>0.8</v>
       </c>
       <c r="G134" t="n">
-        <v>8.039999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="H134" t="n">
         <v>5490</v>
       </c>
       <c r="I134" t="n">
-        <v>-471.3</v>
+        <v>-291.7</v>
       </c>
       <c r="J134" t="n">
         <v>38.8</v>
@@ -13815,19 +13809,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="F135" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G135" t="n">
-        <v>6.54</v>
+        <v>7.29</v>
       </c>
       <c r="H135" t="n">
         <v>30705</v>
       </c>
       <c r="I135" t="n">
-        <v>650.5</v>
+        <v>279.2</v>
       </c>
       <c r="J135" t="n">
         <v>7.1</v>
@@ -13872,13 +13866,13 @@
         </is>
       </c>
       <c r="V135" t="n">
-        <v>3928.5</v>
+        <v>4405.6</v>
       </c>
       <c r="W135" t="n">
         <v>402</v>
       </c>
       <c r="X135" t="n">
-        <v>-497.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Y135" t="inlineStr">
         <is>
@@ -13924,7 +13918,7 @@
         <v>0.6</v>
       </c>
       <c r="G136" t="n">
-        <v>3.36</v>
+        <v>3.21</v>
       </c>
       <c r="H136" t="n">
         <v>1071</v>
@@ -14021,25 +14015,25 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="D137" t="n">
-        <v>12.2</v>
+        <v>11.4</v>
       </c>
       <c r="E137" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="F137" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G137" t="n">
-        <v>3.16</v>
+        <v>2.48</v>
       </c>
       <c r="H137" t="n">
         <v>6817.4</v>
       </c>
       <c r="I137" t="n">
-        <v>-411.4</v>
+        <v>-499.5</v>
       </c>
       <c r="J137" t="n">
         <v>24.9</v>
@@ -14084,13 +14078,13 @@
         </is>
       </c>
       <c r="V137" t="n">
-        <v>4618.5</v>
+        <v>5111.7</v>
       </c>
       <c r="W137" t="n">
         <v>168</v>
       </c>
       <c r="X137" t="n">
-        <v>455.5</v>
+        <v>29.5</v>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
@@ -14227,7 +14221,7 @@
         <v>2.7</v>
       </c>
       <c r="G139" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="H139" t="n">
         <v>43399.8</v>
@@ -14323,23 +14317,20 @@
           <t>Çimbeton Hisse Senedi</t>
         </is>
       </c>
-      <c r="D140" t="n">
-        <v>21</v>
-      </c>
       <c r="E140" t="n">
-        <v>8</v>
+        <v>13.1</v>
       </c>
       <c r="F140" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G140" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H140" t="n">
         <v>3117</v>
       </c>
       <c r="I140" t="n">
-        <v>44.8</v>
+        <v>357.5</v>
       </c>
       <c r="J140" t="n">
         <v>49.5</v>
@@ -14551,7 +14542,7 @@
         <v>2.9</v>
       </c>
       <c r="G142" t="n">
-        <v>12.67</v>
+        <v>12.18</v>
       </c>
       <c r="H142" t="n">
         <v>2420.9</v>
@@ -14651,7 +14642,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G143" t="n">
-        <v>1.04</v>
+        <v>0.88</v>
       </c>
       <c r="H143" t="n">
         <v>1389.7</v>
@@ -14748,13 +14739,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="E144" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="G144" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="H144" t="n">
         <v>9648</v>
@@ -14839,19 +14830,19 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
       <c r="F145" t="n">
         <v>0.4</v>
       </c>
       <c r="G145" t="n">
-        <v>12.72</v>
+        <v>12.6</v>
       </c>
       <c r="H145" t="n">
         <v>17926.7</v>
       </c>
       <c r="I145" t="n">
-        <v>15837.9</v>
+        <v>20909.8</v>
       </c>
       <c r="J145" t="n">
         <v>10.6</v>
@@ -14948,7 +14939,7 @@
         <v>1.6</v>
       </c>
       <c r="G146" t="n">
-        <v>3.63</v>
+        <v>3.36</v>
       </c>
       <c r="H146" t="n">
         <v>1751.3</v>
@@ -15051,7 +15042,7 @@
         <v>15.6</v>
       </c>
       <c r="G147" t="n">
-        <v>5.33</v>
+        <v>5.45</v>
       </c>
       <c r="H147" t="n">
         <v>49952</v>
@@ -15160,7 +15151,7 @@
         <v>2.5</v>
       </c>
       <c r="G148" t="n">
-        <v>10.32</v>
+        <v>10.15</v>
       </c>
       <c r="H148" t="n">
         <v>39508.5</v>
@@ -15266,7 +15257,7 @@
         <v>1.2</v>
       </c>
       <c r="G149" t="n">
-        <v>11.27</v>
+        <v>11.51</v>
       </c>
       <c r="H149" t="n">
         <v>2660</v>
@@ -15363,19 +15354,19 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>26.8</v>
+        <v>23.7</v>
       </c>
       <c r="E150" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G150" t="n">
-        <v>7.58</v>
+        <v>7.03</v>
       </c>
       <c r="H150" t="n">
         <v>27931</v>
       </c>
       <c r="I150" t="n">
-        <v>1519</v>
+        <v>1273.8</v>
       </c>
       <c r="J150" t="n">
         <v>28.7</v>
@@ -15475,7 +15466,7 @@
         <v>0.7</v>
       </c>
       <c r="G151" t="n">
-        <v>4.92</v>
+        <v>5.01</v>
       </c>
       <c r="H151" t="n">
         <v>5204.6</v>
@@ -15581,7 +15572,7 @@
         <v>1.9</v>
       </c>
       <c r="G152" t="n">
-        <v>8.76</v>
+        <v>9.44</v>
       </c>
       <c r="H152" t="n">
         <v>4812.6</v>
@@ -15681,7 +15672,7 @@
         <v>1.1</v>
       </c>
       <c r="G153" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H153" t="n">
         <v>1518</v>
@@ -15787,7 +15778,7 @@
         <v>1.2</v>
       </c>
       <c r="G154" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="H154" t="n">
         <v>2982.9</v>
@@ -15817,10 +15808,10 @@
         <v>13.29</v>
       </c>
       <c r="Q154" t="n">
-        <v>17.25</v>
+        <v>16.1</v>
       </c>
       <c r="R154" t="n">
-        <v>3.96</v>
+        <v>2.81</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -15884,25 +15875,25 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>22.3</v>
+        <v>20.1</v>
       </c>
       <c r="D155" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="E155" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="F155" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G155" t="n">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="H155" t="n">
         <v>2072.5</v>
       </c>
       <c r="I155" t="n">
-        <v>-607.6</v>
+        <v>-419</v>
       </c>
       <c r="J155" t="n">
         <v>27</v>
@@ -16005,7 +15996,7 @@
         <v>1.4</v>
       </c>
       <c r="G156" t="n">
-        <v>16.19</v>
+        <v>16.27</v>
       </c>
       <c r="H156" t="n">
         <v>6884.5</v>
@@ -16102,22 +16093,22 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="E157" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F157" t="n">
         <v>0.1</v>
       </c>
       <c r="G157" t="n">
-        <v>3.31</v>
+        <v>4.12</v>
       </c>
       <c r="H157" t="n">
         <v>1012</v>
       </c>
       <c r="I157" t="n">
-        <v>-17.7</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
         <v>50.9</v>
@@ -16217,7 +16208,7 @@
         <v>0.8</v>
       </c>
       <c r="G158" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="H158" t="n">
         <v>13211.3</v>
@@ -16323,7 +16314,7 @@
         <v>0.2</v>
       </c>
       <c r="G159" t="n">
-        <v>7.76</v>
+        <v>7.74</v>
       </c>
       <c r="H159" t="n">
         <v>2671.5</v>
@@ -16423,7 +16414,7 @@
         <v>0.7</v>
       </c>
       <c r="G160" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H160" t="n">
         <v>10126.2</v>
@@ -16526,7 +16517,7 @@
         <v>0.7</v>
       </c>
       <c r="G161" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="H161" t="n">
         <v>3174.5</v>
@@ -16722,7 +16713,7 @@
         <v>3</v>
       </c>
       <c r="G163" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="H163" t="n">
         <v>5661</v>
@@ -16837,7 +16828,7 @@
         <v>6.9</v>
       </c>
       <c r="G165" t="n">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="H165" t="n">
         <v>8286.6</v>
@@ -16864,13 +16855,13 @@
         <v>-2.31</v>
       </c>
       <c r="P165" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="Q165" t="n">
         <v>5.72</v>
       </c>
       <c r="R165" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -16930,22 +16921,22 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>14.9</v>
+        <v>10.2</v>
       </c>
       <c r="E166" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G166" t="n">
-        <v>7.62</v>
+        <v>7.46</v>
       </c>
       <c r="H166" t="n">
         <v>1818</v>
       </c>
       <c r="I166" t="n">
-        <v>668.6</v>
+        <v>747.7</v>
       </c>
       <c r="J166" t="n">
         <v>52.6</v>
@@ -17036,22 +17027,22 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>26.5</v>
+        <v>25.9</v>
       </c>
       <c r="E167" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F167" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="G167" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="H167" t="n">
         <v>2408.9</v>
       </c>
       <c r="I167" t="n">
-        <v>-112.3</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="J167" t="n">
         <v>44.3</v>
@@ -17239,7 +17230,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="H169" t="n">
         <v>100004.4</v>
@@ -17345,7 +17336,7 @@
         <v>0.2</v>
       </c>
       <c r="G170" t="n">
-        <v>3.49</v>
+        <v>3.68</v>
       </c>
       <c r="H170" t="n">
         <v>1838.6</v>
@@ -17448,7 +17439,7 @@
         <v>22.2</v>
       </c>
       <c r="G171" t="n">
-        <v>9.140000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H171" t="n">
         <v>22351</v>
@@ -17730,7 +17721,7 @@
         <v>1.2</v>
       </c>
       <c r="G174" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="H174" t="n">
         <v>7996.3</v>
@@ -17760,10 +17751,10 @@
         <v>21.74</v>
       </c>
       <c r="Q174" t="n">
-        <v>26.76</v>
+        <v>26.54</v>
       </c>
       <c r="R174" t="n">
-        <v>5.02</v>
+        <v>4.8</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -17827,7 +17818,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>11.49</v>
+        <v>11.33</v>
       </c>
       <c r="H175" t="n">
         <v>910000</v>
@@ -17851,13 +17842,13 @@
         <v>5.15</v>
       </c>
       <c r="P175" t="n">
-        <v>827.5</v>
+        <v>850</v>
       </c>
       <c r="Q175" t="n">
         <v>2810</v>
       </c>
       <c r="R175" t="n">
-        <v>1982.5</v>
+        <v>1960</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -17912,19 +17903,22 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5.6</v>
+        <v>10.9</v>
       </c>
       <c r="E176" t="n">
-        <v>2.8</v>
+        <v>3</v>
+      </c>
+      <c r="F176" t="n">
+        <v>21.8</v>
       </c>
       <c r="G176" t="n">
-        <v>7.04</v>
+        <v>7.06</v>
       </c>
       <c r="H176" t="n">
         <v>4415.2</v>
       </c>
       <c r="I176" t="n">
-        <v>-1604.7</v>
+        <v>-1494.5</v>
       </c>
       <c r="J176" t="n">
         <v>59.1</v>
@@ -18024,7 +18018,7 @@
         <v>1.2</v>
       </c>
       <c r="G177" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="H177" t="n">
         <v>2430</v>
@@ -18120,26 +18114,23 @@
           <t>Durukan Şekerleme Hisse Senedi</t>
         </is>
       </c>
-      <c r="C178" t="n">
-        <v>21.3</v>
-      </c>
       <c r="D178" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="E178" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F178" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G178" t="n">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
       <c r="H178" t="n">
         <v>2917.7</v>
       </c>
       <c r="I178" t="n">
-        <v>900.4</v>
+        <v>1158.4</v>
       </c>
       <c r="J178" t="n">
         <v>32</v>
@@ -18184,13 +18175,13 @@
         </is>
       </c>
       <c r="V178" t="n">
-        <v>2377.5</v>
+        <v>2574.9</v>
       </c>
       <c r="W178" t="n">
         <v>132.5</v>
       </c>
       <c r="X178" t="n">
-        <v>136.7</v>
+        <v>-36.8</v>
       </c>
       <c r="Y178" t="inlineStr">
         <is>
@@ -18239,7 +18230,7 @@
         <v>1.1</v>
       </c>
       <c r="G179" t="n">
-        <v>2.74</v>
+        <v>0.39</v>
       </c>
       <c r="H179" t="n">
         <v>6036</v>
@@ -18342,7 +18333,7 @@
         <v>0.5</v>
       </c>
       <c r="G180" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="H180" t="n">
         <v>3104</v>
@@ -18448,7 +18439,7 @@
         <v>0.4</v>
       </c>
       <c r="G181" t="n">
-        <v>17</v>
+        <v>16.96</v>
       </c>
       <c r="H181" t="n">
         <v>11488</v>
@@ -18554,7 +18545,7 @@
         <v>5.8</v>
       </c>
       <c r="G182" t="n">
-        <v>9.33</v>
+        <v>9.06</v>
       </c>
       <c r="H182" t="n">
         <v>58555.5</v>
@@ -18660,7 +18651,7 @@
         <v>4.6</v>
       </c>
       <c r="G183" t="n">
-        <v>36.92</v>
+        <v>36.85</v>
       </c>
       <c r="H183" t="n">
         <v>20293.2</v>
@@ -18760,7 +18751,7 @@
         <v>1.4</v>
       </c>
       <c r="G184" t="n">
-        <v>4.87</v>
+        <v>4.89</v>
       </c>
       <c r="H184" t="n">
         <v>39375</v>
@@ -18863,7 +18854,7 @@
         <v>3.2</v>
       </c>
       <c r="G185" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="H185" t="n">
         <v>8622.5</v>
@@ -18966,7 +18957,7 @@
         <v>0.4</v>
       </c>
       <c r="G186" t="n">
-        <v>5.95</v>
+        <v>6.12</v>
       </c>
       <c r="H186" t="n">
         <v>2566.2</v>
@@ -19072,7 +19063,7 @@
         <v>2.1</v>
       </c>
       <c r="G187" t="n">
-        <v>28.69</v>
+        <v>26.58</v>
       </c>
       <c r="H187" t="n">
         <v>25155.9</v>
@@ -19175,7 +19166,7 @@
         <v>4.2</v>
       </c>
       <c r="G188" t="n">
-        <v>7.06</v>
+        <v>7.16</v>
       </c>
       <c r="H188" t="n">
         <v>19978.9</v>
@@ -19272,19 +19263,19 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="E189" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="G189" t="n">
-        <v>19.32</v>
+        <v>19.39</v>
       </c>
       <c r="H189" t="n">
         <v>6136</v>
       </c>
       <c r="I189" t="n">
-        <v>-29.6</v>
+        <v>393.9</v>
       </c>
       <c r="J189" t="n">
         <v>34.6</v>
@@ -19329,13 +19320,13 @@
         </is>
       </c>
       <c r="V189" t="n">
-        <v>1715.9</v>
+        <v>2408.8</v>
       </c>
       <c r="W189" t="n">
         <v>200</v>
       </c>
       <c r="X189" t="n">
-        <v>811.9</v>
+        <v>520.8</v>
       </c>
       <c r="Y189" t="inlineStr">
         <is>
@@ -19384,7 +19375,7 @@
         <v>6</v>
       </c>
       <c r="G190" t="n">
-        <v>12.61</v>
+        <v>12.41</v>
       </c>
       <c r="H190" t="n">
         <v>9400</v>
@@ -19411,13 +19402,13 @@
         <v>-2</v>
       </c>
       <c r="P190" t="n">
-        <v>10.52</v>
+        <v>10.79</v>
       </c>
       <c r="Q190" t="n">
         <v>19.01</v>
       </c>
       <c r="R190" t="n">
-        <v>8.49</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -19481,10 +19472,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="D191" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="E191" t="n">
         <v>1.5</v>
@@ -19493,10 +19484,10 @@
         <v>3.5</v>
       </c>
       <c r="G191" t="n">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="H191" t="n">
-        <v>12680</v>
+        <v>12430</v>
       </c>
       <c r="I191" t="n">
         <v>50.3</v>
@@ -19508,7 +19499,7 @@
         <v>-0.31</v>
       </c>
       <c r="L191" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="M191" t="n">
         <v>8.84</v>
@@ -19520,13 +19511,13 @@
         <v>-1.22</v>
       </c>
       <c r="P191" t="n">
-        <v>87.05</v>
+        <v>85.33369999999999</v>
       </c>
       <c r="Q191" t="n">
-        <v>131.6</v>
+        <v>129.0054</v>
       </c>
       <c r="R191" t="n">
-        <v>44.55</v>
+        <v>43.6717</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -19602,7 +19593,7 @@
         <v>1.9</v>
       </c>
       <c r="G192" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H192" t="n">
         <v>24252.5</v>
@@ -19705,13 +19696,13 @@
         <v>0.8</v>
       </c>
       <c r="G193" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="H193" t="n">
         <v>2196</v>
       </c>
       <c r="I193" t="n">
-        <v>1509.1</v>
+        <v>2110.5</v>
       </c>
       <c r="J193" t="n">
         <v>34.3</v>
@@ -19821,7 +19812,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -19881,7 +19872,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="F195" t="n">
         <v>2.1</v>
@@ -19911,10 +19902,10 @@
         <v>91</v>
       </c>
       <c r="Q195" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R195" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -19984,7 +19975,7 @@
         <v>3</v>
       </c>
       <c r="G196" t="n">
-        <v>3.07</v>
+        <v>2.33</v>
       </c>
       <c r="H196" t="n">
         <v>6921.6</v>
@@ -20090,7 +20081,7 @@
         <v>0.5</v>
       </c>
       <c r="G197" t="n">
-        <v>12.8</v>
+        <v>12.84</v>
       </c>
       <c r="H197" t="n">
         <v>3552</v>
@@ -20199,7 +20190,7 @@
         <v>1.8</v>
       </c>
       <c r="G198" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="H198" t="n">
         <v>3965.8</v>
@@ -20302,7 +20293,7 @@
         <v>4.9</v>
       </c>
       <c r="G199" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="H199" t="n">
         <v>3912</v>
@@ -20399,10 +20390,10 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H200" t="n">
         <v>926.3</v>
@@ -20508,7 +20499,7 @@
         <v>1.8</v>
       </c>
       <c r="G201" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="H201" t="n">
         <v>6582.4</v>
@@ -20611,7 +20602,7 @@
         <v>4.7</v>
       </c>
       <c r="G202" t="n">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
       <c r="H202" t="n">
         <v>6855.3</v>
@@ -20720,7 +20711,7 @@
         <v>2.4</v>
       </c>
       <c r="G203" t="n">
-        <v>11.99</v>
+        <v>11.93</v>
       </c>
       <c r="H203" t="n">
         <v>80100</v>
@@ -20993,7 +20984,7 @@
         <v>18.1</v>
       </c>
       <c r="G206" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="H206" t="n">
         <v>7971.6</v>
@@ -21178,7 +21169,7 @@
         <v>0.6</v>
       </c>
       <c r="G208" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="H208" t="n">
         <v>1183.7</v>
@@ -21284,7 +21275,7 @@
         <v>0.8</v>
       </c>
       <c r="G209" t="n">
-        <v>5.49</v>
+        <v>5.51</v>
       </c>
       <c r="H209" t="n">
         <v>3934</v>
@@ -21390,7 +21381,7 @@
         <v>1.4</v>
       </c>
       <c r="G210" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="H210" t="n">
         <v>4522.4</v>
@@ -21572,19 +21563,19 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F212" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="G212" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H212" t="n">
         <v>950.4</v>
       </c>
       <c r="I212" t="n">
-        <v>-84.5</v>
+        <v>-139.1</v>
       </c>
       <c r="J212" t="n">
         <v>65.40000000000001</v>
@@ -21681,7 +21672,7 @@
         <v>6.8</v>
       </c>
       <c r="G213" t="n">
-        <v>33.68</v>
+        <v>33.75</v>
       </c>
       <c r="H213" t="n">
         <v>26075</v>
@@ -21790,7 +21781,7 @@
         <v>1.7</v>
       </c>
       <c r="G214" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="H214" t="n">
         <v>3876.6</v>
@@ -21817,13 +21808,13 @@
         <v>-6.52</v>
       </c>
       <c r="P214" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="Q214" t="n">
         <v>6.65</v>
       </c>
       <c r="R214" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -21896,7 +21887,7 @@
         <v>7.3</v>
       </c>
       <c r="G215" t="n">
-        <v>4.54</v>
+        <v>4.61</v>
       </c>
       <c r="H215" t="n">
         <v>6788.6</v>
@@ -22002,7 +21993,7 @@
         <v>0.8</v>
       </c>
       <c r="G216" t="n">
-        <v>2.08</v>
+        <v>0.27</v>
       </c>
       <c r="H216" t="n">
         <v>1236</v>
@@ -22105,7 +22096,7 @@
         <v>7</v>
       </c>
       <c r="G217" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H217" t="n">
         <v>481.2</v>
@@ -22202,7 +22193,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E218" t="n">
         <v>0.4</v>
@@ -22214,7 +22205,7 @@
         <v>1942.5</v>
       </c>
       <c r="I218" t="n">
-        <v>-3.9</v>
+        <v>-3.3</v>
       </c>
       <c r="J218" t="n">
         <v>88.40000000000001</v>
@@ -22311,7 +22302,7 @@
         <v>5.6</v>
       </c>
       <c r="G219" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="H219" t="n">
         <v>450.6</v>
@@ -22338,13 +22329,13 @@
         <v>-0.38</v>
       </c>
       <c r="P219" t="n">
-        <v>5.28</v>
+        <v>5.4767</v>
       </c>
       <c r="Q219" t="n">
         <v>7.92</v>
       </c>
       <c r="R219" t="n">
-        <v>2.64</v>
+        <v>2.4433</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -22417,7 +22408,7 @@
         <v>2.8</v>
       </c>
       <c r="G220" t="n">
-        <v>15.42</v>
+        <v>18.36</v>
       </c>
       <c r="H220" t="n">
         <v>34584</v>
@@ -22514,25 +22505,25 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>13.9</v>
+        <v>23.5</v>
       </c>
       <c r="D221" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="E221" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G221" t="n">
-        <v>9.880000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H221" t="n">
         <v>11571</v>
       </c>
       <c r="I221" t="n">
-        <v>1385.2</v>
+        <v>1185.9</v>
       </c>
       <c r="J221" t="n">
         <v>49.5</v>
@@ -22629,7 +22620,7 @@
         <v>4.3</v>
       </c>
       <c r="G222" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H222" t="n">
         <v>354</v>
@@ -22656,13 +22647,13 @@
         <v>4.21</v>
       </c>
       <c r="P222" t="n">
-        <v>5.19</v>
+        <v>5.4767</v>
       </c>
       <c r="Q222" t="n">
         <v>6.4933</v>
       </c>
       <c r="R222" t="n">
-        <v>1.3033</v>
+        <v>1.0167</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -22729,7 +22720,7 @@
         <v>1.1</v>
       </c>
       <c r="G223" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="H223" t="n">
         <v>1953</v>
@@ -22838,7 +22829,7 @@
         <v>1.4</v>
       </c>
       <c r="G224" t="n">
-        <v>6.61</v>
+        <v>5.96</v>
       </c>
       <c r="H224" t="n">
         <v>1253.4</v>
@@ -22941,7 +22932,7 @@
         <v>2.1</v>
       </c>
       <c r="G225" t="n">
-        <v>8.23</v>
+        <v>7.79</v>
       </c>
       <c r="H225" t="n">
         <v>19625</v>
@@ -23038,10 +23029,10 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F226" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="G226" t="n">
         <v>1.21</v>
@@ -23050,7 +23041,7 @@
         <v>1318.1</v>
       </c>
       <c r="I226" t="n">
-        <v>-9.1</v>
+        <v>-21.1</v>
       </c>
       <c r="J226" t="n">
         <v>74.5</v>
@@ -23153,7 +23144,7 @@
         <v>5.2</v>
       </c>
       <c r="G227" t="n">
-        <v>5.22</v>
+        <v>3.37</v>
       </c>
       <c r="H227" t="n">
         <v>4218.8</v>
@@ -23262,7 +23253,7 @@
         <v>5.3</v>
       </c>
       <c r="G228" t="n">
-        <v>1.16</v>
+        <v>0.97</v>
       </c>
       <c r="H228" t="n">
         <v>4595.8</v>
@@ -23359,19 +23350,19 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F229" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G229" t="n">
-        <v>7.33</v>
+        <v>6.91</v>
       </c>
       <c r="H229" t="n">
         <v>3136.6</v>
       </c>
       <c r="I229" t="n">
-        <v>100.5</v>
+        <v>105</v>
       </c>
       <c r="J229" t="n">
         <v>90.09999999999999</v>
@@ -23474,7 +23465,7 @@
         <v>3.1</v>
       </c>
       <c r="G230" t="n">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="H230" t="n">
         <v>6324.8</v>
@@ -23573,7 +23564,7 @@
         <v>2.4</v>
       </c>
       <c r="G231" t="n">
-        <v>5.75</v>
+        <v>6.17</v>
       </c>
       <c r="H231" t="n">
         <v>2715.5</v>
@@ -23682,7 +23673,7 @@
         <v>1.5</v>
       </c>
       <c r="G232" t="n">
-        <v>1.28</v>
+        <v>0.82</v>
       </c>
       <c r="H232" t="n">
         <v>5289.6</v>
@@ -23709,10 +23700,10 @@
         <v>28.44</v>
       </c>
       <c r="Q232" t="n">
-        <v>42.72</v>
+        <v>40.5</v>
       </c>
       <c r="R232" t="n">
-        <v>14.28</v>
+        <v>12.06</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -23864,7 +23855,7 @@
         <v>4.5</v>
       </c>
       <c r="G234" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="H234" t="n">
         <v>18487.5</v>
@@ -23973,10 +23964,10 @@
         <v>120.6254</v>
       </c>
       <c r="Q235" t="n">
-        <v>158.5912</v>
+        <v>157.5339</v>
       </c>
       <c r="R235" t="n">
-        <v>37.9658</v>
+        <v>36.9085</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -24046,7 +24037,7 @@
         <v>1.9</v>
       </c>
       <c r="G236" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="H236" t="n">
         <v>11177.7</v>
@@ -24130,17 +24121,20 @@
           <t>Gate Group Hisse Senedi</t>
         </is>
       </c>
+      <c r="D237" t="n">
+        <v>28.8</v>
+      </c>
       <c r="E237" t="n">
-        <v>13.6</v>
+        <v>11.5</v>
       </c>
       <c r="F237" t="n">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="H237" t="n">
         <v>3588.5</v>
       </c>
       <c r="I237" t="n">
-        <v>130.4</v>
+        <v>90.8</v>
       </c>
       <c r="J237" t="n">
         <v>71</v>
@@ -24185,13 +24179,13 @@
         </is>
       </c>
       <c r="V237" t="n">
-        <v>263.8</v>
+        <v>311.5</v>
       </c>
       <c r="W237" t="n">
-        <v>7.8</v>
+        <v>11.3</v>
       </c>
       <c r="X237" t="n">
-        <v>31.7</v>
+        <v>16</v>
       </c>
       <c r="Y237" t="inlineStr">
         <is>
@@ -24243,7 +24237,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H238" t="n">
         <v>11420</v>
@@ -24349,7 +24343,7 @@
         <v>1.1</v>
       </c>
       <c r="G239" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="H239" t="n">
         <v>1382.9</v>
@@ -24451,7 +24445,7 @@
         <v>2.2</v>
       </c>
       <c r="G240" t="n">
-        <v>9.550000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="H240" t="n">
         <v>41670</v>
@@ -24556,7 +24550,7 @@
         <v>1.9</v>
       </c>
       <c r="G241" t="n">
-        <v>1.84</v>
+        <v>3.18</v>
       </c>
       <c r="H241" t="n">
         <v>8513.799999999999</v>
@@ -24662,7 +24656,7 @@
         <v>1.1</v>
       </c>
       <c r="G242" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="H242" t="n">
         <v>5955</v>
@@ -24692,10 +24686,10 @@
         <v>7</v>
       </c>
       <c r="Q242" t="n">
-        <v>12.31</v>
+        <v>11.29</v>
       </c>
       <c r="R242" t="n">
-        <v>5.31</v>
+        <v>4.29</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -24765,7 +24759,7 @@
         <v>5.7</v>
       </c>
       <c r="G243" t="n">
-        <v>5.17</v>
+        <v>5.42</v>
       </c>
       <c r="H243" t="n">
         <v>14347.8</v>
@@ -24874,7 +24868,7 @@
         <v>1.3</v>
       </c>
       <c r="G244" t="n">
-        <v>10.4</v>
+        <v>10.96</v>
       </c>
       <c r="H244" t="n">
         <v>22908</v>
@@ -24971,22 +24965,22 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>24.2</v>
+        <v>21.5</v>
       </c>
       <c r="E245" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F245" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="G245" t="n">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="H245" t="n">
         <v>11543.4</v>
       </c>
       <c r="I245" t="n">
-        <v>-1645</v>
+        <v>-1990</v>
       </c>
       <c r="J245" t="n">
         <v>39.1</v>
@@ -25077,22 +25071,22 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>18.8</v>
+        <v>22</v>
       </c>
       <c r="E246" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F246" t="n">
         <v>0.1</v>
       </c>
       <c r="G246" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="H246" t="n">
         <v>1447.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-13.3</v>
+        <v>38.6</v>
       </c>
       <c r="J246" t="n">
         <v>24.3</v>
@@ -25192,7 +25186,7 @@
         <v>1.4</v>
       </c>
       <c r="G247" t="n">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
       <c r="H247" t="n">
         <v>9199.200000000001</v>
@@ -25289,7 +25283,7 @@
         <v>1.3</v>
       </c>
       <c r="G248" t="n">
-        <v>20.12</v>
+        <v>18.61</v>
       </c>
       <c r="H248" t="n">
         <v>61132.7</v>
@@ -25392,7 +25386,7 @@
         <v>0.5</v>
       </c>
       <c r="G249" t="n">
-        <v>7.43</v>
+        <v>7.53</v>
       </c>
       <c r="H249" t="n">
         <v>2388</v>
@@ -25495,7 +25489,7 @@
         <v>2.1</v>
       </c>
       <c r="G250" t="n">
-        <v>23.8</v>
+        <v>23.79</v>
       </c>
       <c r="H250" t="n">
         <v>29835</v>
@@ -25601,7 +25595,7 @@
         <v>2.1</v>
       </c>
       <c r="G251" t="n">
-        <v>32.79</v>
+        <v>32.92</v>
       </c>
       <c r="H251" t="n">
         <v>12786</v>
@@ -25628,13 +25622,13 @@
         <v>1.91</v>
       </c>
       <c r="P251" t="n">
-        <v>24.44</v>
+        <v>25.18</v>
       </c>
       <c r="Q251" t="n">
         <v>51</v>
       </c>
       <c r="R251" t="n">
-        <v>26.56</v>
+        <v>25.82</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -25795,7 +25789,7 @@
         <v>1.3</v>
       </c>
       <c r="G253" t="n">
-        <v>8.460000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="H253" t="n">
         <v>6592.5</v>
@@ -25901,7 +25895,7 @@
         <v>0.2</v>
       </c>
       <c r="G254" t="n">
-        <v>49.74</v>
+        <v>49.7</v>
       </c>
       <c r="H254" t="n">
         <v>4195.8</v>
@@ -26001,7 +25995,7 @@
         <v>0.3</v>
       </c>
       <c r="G255" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H255" t="n">
         <v>7696.1</v>
@@ -26213,7 +26207,7 @@
         <v>2.5</v>
       </c>
       <c r="G257" t="n">
-        <v>7.51</v>
+        <v>7.42</v>
       </c>
       <c r="H257" t="n">
         <v>30498</v>
@@ -26322,7 +26316,7 @@
         <v>4.3</v>
       </c>
       <c r="G258" t="n">
-        <v>13.1</v>
+        <v>13.16</v>
       </c>
       <c r="H258" t="n">
         <v>32250</v>
@@ -26349,13 +26343,13 @@
         <v>0.64</v>
       </c>
       <c r="P258" t="n">
-        <v>214</v>
+        <v>225.2</v>
       </c>
       <c r="Q258" t="n">
         <v>281.75</v>
       </c>
       <c r="R258" t="n">
-        <v>67.75</v>
+        <v>56.55</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -26431,7 +26425,7 @@
         <v>3.5</v>
       </c>
       <c r="G259" t="n">
-        <v>8.02</v>
+        <v>8.24</v>
       </c>
       <c r="H259" t="n">
         <v>1963.5</v>
@@ -26534,7 +26528,7 @@
         <v>0.4</v>
       </c>
       <c r="G260" t="n">
-        <v>16.65</v>
+        <v>16.84</v>
       </c>
       <c r="H260" t="n">
         <v>5270</v>
@@ -26640,7 +26634,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="H261" t="n">
         <v>15795</v>
@@ -26749,7 +26743,7 @@
         <v>3.4</v>
       </c>
       <c r="G262" t="n">
-        <v>12.35</v>
+        <v>12.07</v>
       </c>
       <c r="H262" t="n">
         <v>177187</v>
@@ -26846,16 +26840,16 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="G263" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="H263" t="n">
         <v>36016.5</v>
       </c>
       <c r="I263" t="n">
-        <v>84.3</v>
+        <v>-624</v>
       </c>
       <c r="J263" t="n">
         <v>15.5</v>
@@ -26876,13 +26870,13 @@
         <v>1.67</v>
       </c>
       <c r="P263" t="n">
-        <v>214.8</v>
+        <v>233.8</v>
       </c>
       <c r="Q263" t="n">
         <v>923.5</v>
       </c>
       <c r="R263" t="n">
-        <v>708.7</v>
+        <v>689.7</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -26900,13 +26894,13 @@
         </is>
       </c>
       <c r="V263" t="n">
-        <v>786.2</v>
+        <v>832.6</v>
       </c>
       <c r="W263" t="n">
         <v>39</v>
       </c>
       <c r="X263" t="n">
-        <v>-103.9</v>
+        <v>-34.6</v>
       </c>
       <c r="Y263" t="inlineStr">
         <is>
@@ -27040,7 +27034,7 @@
         <v>1.7</v>
       </c>
       <c r="G265" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H265" t="n">
         <v>4618.3</v>
@@ -27222,7 +27216,7 @@
         <v>2.5</v>
       </c>
       <c r="G267" t="n">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="H267" t="n">
         <v>1072.9</v>
@@ -27325,7 +27319,7 @@
         <v>2</v>
       </c>
       <c r="G268" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="H268" t="n">
         <v>9746</v>
@@ -27418,25 +27412,25 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>13.2</v>
+        <v>6.1</v>
       </c>
       <c r="D269" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E269" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F269" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G269" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H269" t="n">
         <v>3921.1</v>
       </c>
       <c r="I269" t="n">
-        <v>-16.4</v>
+        <v>-13.5</v>
       </c>
       <c r="J269" t="n">
         <v>78.7</v>
@@ -27527,13 +27521,13 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H270" t="n">
         <v>290468.9</v>
       </c>
       <c r="I270" t="n">
-        <v>-22.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J270" t="n">
         <v>8</v>
@@ -27554,13 +27548,13 @@
         <v>-1.24</v>
       </c>
       <c r="P270" t="n">
-        <v>50.95</v>
+        <v>60.5</v>
       </c>
       <c r="Q270" t="n">
         <v>151</v>
       </c>
       <c r="R270" t="n">
-        <v>100.05</v>
+        <v>90.5</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -27630,7 +27624,7 @@
         <v>6.1</v>
       </c>
       <c r="G271" t="n">
-        <v>12.03</v>
+        <v>12.06</v>
       </c>
       <c r="H271" t="n">
         <v>28914.9</v>
@@ -27736,7 +27730,7 @@
         <v>2.5</v>
       </c>
       <c r="G272" t="n">
-        <v>0.65</v>
+        <v>1.24</v>
       </c>
       <c r="H272" t="n">
         <v>1644.3</v>
@@ -27831,7 +27825,7 @@
         <v>0.4</v>
       </c>
       <c r="G273" t="n">
-        <v>6.51</v>
+        <v>6.01</v>
       </c>
       <c r="H273" t="n">
         <v>22387.2</v>
@@ -27937,7 +27931,7 @@
         <v>0.8</v>
       </c>
       <c r="G274" t="n">
-        <v>6.03</v>
+        <v>4.1</v>
       </c>
       <c r="H274" t="n">
         <v>7537.7</v>
@@ -28043,7 +28037,7 @@
         <v>2.4</v>
       </c>
       <c r="G275" t="n">
-        <v>5.88</v>
+        <v>6.07</v>
       </c>
       <c r="H275" t="n">
         <v>8593.9</v>
@@ -28228,7 +28222,7 @@
         <v>2.1</v>
       </c>
       <c r="G277" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="H277" t="n">
         <v>1097.6</v>
@@ -28255,13 +28249,13 @@
         <v>-3.62</v>
       </c>
       <c r="P277" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="Q277" t="n">
         <v>5.15</v>
       </c>
       <c r="R277" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -28334,7 +28328,7 @@
         <v>5.4</v>
       </c>
       <c r="G278" t="n">
-        <v>8.58</v>
+        <v>8.59</v>
       </c>
       <c r="H278" t="n">
         <v>3200</v>
@@ -28437,7 +28431,7 @@
         <v>4</v>
       </c>
       <c r="G279" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="H279" t="n">
         <v>4706.4</v>
@@ -28540,7 +28534,7 @@
         <v>3.1</v>
       </c>
       <c r="G280" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="H280" t="n">
         <v>14465.2</v>
@@ -28634,16 +28628,16 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G281" t="n">
-        <v>8.02</v>
+        <v>8.65</v>
       </c>
       <c r="H281" t="n">
         <v>1973.8</v>
       </c>
       <c r="I281" t="n">
-        <v>33.4</v>
+        <v>35.3</v>
       </c>
       <c r="J281" t="n">
         <v>96.7</v>
@@ -28734,19 +28728,19 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="E282" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G282" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="H282" t="n">
         <v>493.5</v>
       </c>
       <c r="I282" t="n">
-        <v>247.7</v>
+        <v>325</v>
       </c>
       <c r="J282" t="n">
         <v>76.5</v>
@@ -28840,7 +28834,7 @@
         <v>23.7</v>
       </c>
       <c r="G283" t="n">
-        <v>12.25</v>
+        <v>12.17</v>
       </c>
       <c r="H283" t="n">
         <v>53843.2</v>
@@ -28867,13 +28861,13 @@
         <v>-0.61</v>
       </c>
       <c r="P283" t="n">
-        <v>76.15000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Q283" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="R283" t="n">
-        <v>22.95</v>
+        <v>22.5</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -28936,20 +28930,17 @@
           <t>İhlas Haber Ajansı Hisse Senedi</t>
         </is>
       </c>
-      <c r="E284" t="n">
-        <v>37.5</v>
-      </c>
       <c r="F284" t="n">
-        <v>23.2</v>
+        <v>21.2</v>
       </c>
       <c r="G284" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="H284" t="n">
         <v>12714</v>
       </c>
       <c r="I284" t="n">
-        <v>-12</v>
+        <v>-15.5</v>
       </c>
       <c r="J284" t="n">
         <v>34.4</v>
@@ -29149,22 +29140,22 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="E286" t="n">
         <v>0.3</v>
       </c>
       <c r="F286" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G286" t="n">
-        <v>7.31</v>
+        <v>7.54</v>
       </c>
       <c r="H286" t="n">
         <v>1224</v>
       </c>
       <c r="I286" t="n">
-        <v>-97.59999999999999</v>
+        <v>-123.9</v>
       </c>
       <c r="J286" t="n">
         <v>59.4</v>
@@ -29258,7 +29249,7 @@
         <v>1.2</v>
       </c>
       <c r="G287" t="n">
-        <v>16.06</v>
+        <v>16.26</v>
       </c>
       <c r="H287" t="n">
         <v>3360</v>
@@ -29361,7 +29352,7 @@
         <v>1.3</v>
       </c>
       <c r="G288" t="n">
-        <v>15.59</v>
+        <v>15.51</v>
       </c>
       <c r="H288" t="n">
         <v>2240</v>
@@ -29464,7 +29455,7 @@
         <v>0.2</v>
       </c>
       <c r="G289" t="n">
-        <v>4.54</v>
+        <v>4.31</v>
       </c>
       <c r="H289" t="n">
         <v>814.5</v>
@@ -29570,7 +29561,7 @@
         <v>1.6</v>
       </c>
       <c r="G290" t="n">
-        <v>6.33</v>
+        <v>5.79</v>
       </c>
       <c r="H290" t="n">
         <v>3431.8</v>
@@ -29679,7 +29670,7 @@
         <v>0.1</v>
       </c>
       <c r="G291" t="n">
-        <v>14.42</v>
+        <v>14.35</v>
       </c>
       <c r="H291" t="n">
         <v>7650</v>
@@ -29782,7 +29773,7 @@
         <v>1.1</v>
       </c>
       <c r="G292" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="H292" t="n">
         <v>3294</v>
@@ -29888,7 +29879,7 @@
         <v>0.6</v>
       </c>
       <c r="G293" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H293" t="n">
         <v>10290</v>
@@ -30088,22 +30079,22 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>19.3</v>
+        <v>15</v>
       </c>
       <c r="E295" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="F295" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G295" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="H295" t="n">
         <v>5608.4</v>
       </c>
       <c r="I295" t="n">
-        <v>55.2</v>
+        <v>57</v>
       </c>
       <c r="J295" t="n">
         <v>12.6</v>
@@ -30193,17 +30184,20 @@
           <t>İnveo Yatırım Holding Hisse Senedi</t>
         </is>
       </c>
+      <c r="C296" t="n">
+        <v>33.6</v>
+      </c>
       <c r="E296" t="n">
         <v>0.7</v>
       </c>
       <c r="G296" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H296" t="n">
         <v>7620</v>
       </c>
       <c r="I296" t="n">
-        <v>2496.2</v>
+        <v>4033.7</v>
       </c>
       <c r="J296" t="n">
         <v>18.9</v>
@@ -30293,17 +30287,20 @@
           <t>Investco Holding Hisse Senedi</t>
         </is>
       </c>
+      <c r="C297" t="n">
+        <v>31.2</v>
+      </c>
       <c r="E297" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="G297" t="n">
-        <v>8.77</v>
+        <v>8.93</v>
       </c>
       <c r="H297" t="n">
         <v>103312.5</v>
       </c>
       <c r="I297" t="n">
-        <v>-3693.4</v>
+        <v>-3513.7</v>
       </c>
       <c r="J297" t="n">
         <v>20</v>
@@ -30767,7 +30764,7 @@
         <v>0.9</v>
       </c>
       <c r="G302" t="n">
-        <v>16.98</v>
+        <v>16.96</v>
       </c>
       <c r="H302" t="n">
         <v>140418</v>
@@ -30794,13 +30791,13 @@
         <v>-0.62</v>
       </c>
       <c r="P302" t="n">
-        <v>40.72</v>
+        <v>41</v>
       </c>
       <c r="Q302" t="n">
         <v>48.42</v>
       </c>
       <c r="R302" t="n">
-        <v>7.7</v>
+        <v>7.42</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
@@ -30870,7 +30867,7 @@
         <v>1.1</v>
       </c>
       <c r="G303" t="n">
-        <v>15.06</v>
+        <v>15.12</v>
       </c>
       <c r="H303" t="n">
         <v>13906.1</v>
@@ -30967,7 +30964,7 @@
         <v>1.9</v>
       </c>
       <c r="G304" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="H304" t="n">
         <v>10248.4</v>
@@ -30994,13 +30991,13 @@
         <v>-6.28</v>
       </c>
       <c r="P304" t="n">
-        <v>73.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q304" t="n">
         <v>149.5</v>
       </c>
       <c r="R304" t="n">
-        <v>75.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -31149,7 +31146,7 @@
         <v>13</v>
       </c>
       <c r="G306" t="n">
-        <v>7.21</v>
+        <v>7.41</v>
       </c>
       <c r="H306" t="n">
         <v>31500</v>
@@ -31270,7 +31267,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>28.95</v>
+        <v>28.96</v>
       </c>
       <c r="H308" t="n">
         <v>63420</v>
@@ -31376,7 +31373,7 @@
         <v>1.3</v>
       </c>
       <c r="G309" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="H309" t="n">
         <v>3539.5</v>
@@ -31482,7 +31479,7 @@
         <v>0.6</v>
       </c>
       <c r="G310" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="H310" t="n">
         <v>1353.9</v>
@@ -31578,26 +31575,23 @@
           <t>İzdemir Enerji Hisse Senedi</t>
         </is>
       </c>
-      <c r="C311" t="n">
-        <v>37.7</v>
-      </c>
       <c r="D311" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="E311" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F311" t="n">
         <v>2.8</v>
       </c>
       <c r="G311" t="n">
-        <v>14.33</v>
+        <v>15.14</v>
       </c>
       <c r="H311" t="n">
         <v>26197</v>
       </c>
       <c r="I311" t="n">
-        <v>-724.7</v>
+        <v>325</v>
       </c>
       <c r="J311" t="n">
         <v>37.4</v>
@@ -31694,7 +31688,7 @@
         <v>27.6</v>
       </c>
       <c r="G312" t="n">
-        <v>7.84</v>
+        <v>7.98</v>
       </c>
       <c r="H312" t="n">
         <v>12146.2</v>
@@ -31797,7 +31791,7 @@
         <v>14.7</v>
       </c>
       <c r="G313" t="n">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="H313" t="n">
         <v>1199.6</v>
@@ -31903,7 +31897,7 @@
         <v>0.5</v>
       </c>
       <c r="G314" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="H314" t="n">
         <v>10545</v>
@@ -32000,22 +31994,22 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="E315" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G315" t="n">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="H315" t="n">
         <v>12369</v>
       </c>
       <c r="I315" t="n">
-        <v>2.4</v>
+        <v>109.2</v>
       </c>
       <c r="J315" t="n">
         <v>17.1</v>
@@ -32060,13 +32054,13 @@
         </is>
       </c>
       <c r="V315" t="n">
-        <v>6605.4</v>
+        <v>7154.3</v>
       </c>
       <c r="W315" t="n">
         <v>700</v>
       </c>
       <c r="X315" t="n">
-        <v>-80.8</v>
+        <v>-117.3</v>
       </c>
       <c r="Y315" t="inlineStr">
         <is>
@@ -32218,7 +32212,7 @@
         <v>0.8</v>
       </c>
       <c r="G317" t="n">
-        <v>17.49</v>
+        <v>17.59</v>
       </c>
       <c r="H317" t="n">
         <v>9509.4</v>
@@ -32324,7 +32318,7 @@
         <v>1.1</v>
       </c>
       <c r="G318" t="n">
-        <v>5.06</v>
+        <v>5.1</v>
       </c>
       <c r="H318" t="n">
         <v>10377</v>
@@ -32536,7 +32530,7 @@
         <v>3.5</v>
       </c>
       <c r="G320" t="n">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="H320" t="n">
         <v>6179.8</v>
@@ -32642,7 +32636,7 @@
         <v>0.9</v>
       </c>
       <c r="G321" t="n">
-        <v>10.48</v>
+        <v>10.41</v>
       </c>
       <c r="H321" t="n">
         <v>14190</v>
@@ -32739,25 +32733,25 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D322" t="n">
         <v>23.7</v>
       </c>
       <c r="E322" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="F322" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="G322" t="n">
-        <v>9.4</v>
+        <v>9.41</v>
       </c>
       <c r="H322" t="n">
         <v>16080</v>
       </c>
       <c r="I322" t="n">
-        <v>3280.4</v>
+        <v>3382</v>
       </c>
       <c r="J322" t="n">
         <v>24</v>
@@ -32778,13 +32772,13 @@
         <v>-0.61</v>
       </c>
       <c r="P322" t="n">
-        <v>16.35</v>
+        <v>17.35</v>
       </c>
       <c r="Q322" t="n">
         <v>26.8</v>
       </c>
       <c r="R322" t="n">
-        <v>10.45</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
@@ -32802,13 +32796,13 @@
         </is>
       </c>
       <c r="V322" t="n">
-        <v>4447.2</v>
+        <v>5131.3</v>
       </c>
       <c r="W322" t="n">
         <v>600</v>
       </c>
       <c r="X322" t="n">
-        <v>643.6</v>
+        <v>230</v>
       </c>
       <c r="Y322" t="inlineStr">
         <is>
@@ -32857,7 +32851,7 @@
         <v>1</v>
       </c>
       <c r="G323" t="n">
-        <v>12.54</v>
+        <v>11.96</v>
       </c>
       <c r="H323" t="n">
         <v>22463</v>
@@ -33030,10 +33024,10 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>19.6</v>
+        <v>18.4</v>
       </c>
       <c r="F325" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -33042,7 +33036,7 @@
         <v>133732.5</v>
       </c>
       <c r="I325" t="n">
-        <v>-1389</v>
+        <v>380.7</v>
       </c>
       <c r="J325" t="n">
         <v>0.5</v>
@@ -33233,7 +33227,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="D327" t="n">
         <v>5.9</v>
@@ -33245,10 +33239,10 @@
         <v>0.5</v>
       </c>
       <c r="G327" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H327" t="n">
-        <v>1720.2</v>
+        <v>1716.3</v>
       </c>
       <c r="I327" t="n">
         <v>-353.2</v>
@@ -33257,28 +33251,28 @@
         <v>74.7</v>
       </c>
       <c r="K327" t="n">
-        <v>-2.13</v>
+        <v>-2.14</v>
       </c>
       <c r="L327" t="n">
         <v>-0.23</v>
       </c>
       <c r="M327" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="N327" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="O327" t="n">
-        <v>-3.02</v>
+        <v>-3.03</v>
       </c>
       <c r="P327" t="n">
-        <v>8.119999999999999</v>
+        <v>8.101100000000001</v>
       </c>
       <c r="Q327" t="n">
-        <v>10.7</v>
+        <v>10.6751</v>
       </c>
       <c r="R327" t="n">
-        <v>2.58</v>
+        <v>2.574</v>
       </c>
       <c r="S327" t="inlineStr">
         <is>
@@ -33345,7 +33339,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G328" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="H328" t="n">
         <v>11150</v>
@@ -33442,25 +33436,25 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="D329" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E329" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F329" t="n">
         <v>0.3</v>
       </c>
       <c r="G329" t="n">
-        <v>13.25</v>
+        <v>10.81</v>
       </c>
       <c r="H329" t="n">
         <v>4070.4</v>
       </c>
       <c r="I329" t="n">
-        <v>670.8</v>
+        <v>464.9</v>
       </c>
       <c r="J329" t="n">
         <v>27.1</v>
@@ -33554,7 +33548,7 @@
         <v>0.3</v>
       </c>
       <c r="G330" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="H330" t="n">
         <v>7254</v>
@@ -33663,7 +33657,7 @@
         <v>1.3</v>
       </c>
       <c r="G331" t="n">
-        <v>13.83</v>
+        <v>14.02</v>
       </c>
       <c r="H331" t="n">
         <v>15676.8</v>
@@ -33769,7 +33763,7 @@
         <v>0.8</v>
       </c>
       <c r="G332" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="H332" t="n">
         <v>2760.9</v>
@@ -33866,10 +33860,10 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>10.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E333" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G333" t="n">
         <v>4.71</v>
@@ -33896,13 +33890,13 @@
         <v>-1.63</v>
       </c>
       <c r="P333" t="n">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="Q333" t="n">
         <v>13.38</v>
       </c>
       <c r="R333" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
@@ -33969,7 +33963,7 @@
         <v>5.1</v>
       </c>
       <c r="G334" t="n">
-        <v>15.75</v>
+        <v>15.89</v>
       </c>
       <c r="H334" t="n">
         <v>166237.5</v>
@@ -34072,7 +34066,7 @@
         <v>1.4</v>
       </c>
       <c r="G335" t="n">
-        <v>6.29</v>
+        <v>6.24</v>
       </c>
       <c r="H335" t="n">
         <v>13610.7</v>
@@ -34178,7 +34172,7 @@
         <v>2.9</v>
       </c>
       <c r="G336" t="n">
-        <v>14.86</v>
+        <v>17.34</v>
       </c>
       <c r="H336" t="n">
         <v>5763.8</v>
@@ -34205,13 +34199,13 @@
         <v>-2.52</v>
       </c>
       <c r="P336" t="n">
-        <v>7.22</v>
+        <v>7.43</v>
       </c>
       <c r="Q336" t="n">
         <v>13.58</v>
       </c>
       <c r="R336" t="n">
-        <v>6.36</v>
+        <v>6.15</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
@@ -34275,22 +34269,22 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>17.7</v>
+        <v>18.9</v>
       </c>
       <c r="E337" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F337" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G337" t="n">
-        <v>8.1</v>
+        <v>7.84</v>
       </c>
       <c r="H337" t="n">
         <v>24254.4</v>
       </c>
       <c r="I337" t="n">
-        <v>14071.8</v>
+        <v>13556.7</v>
       </c>
       <c r="J337" t="n">
         <v>11.3</v>
@@ -34335,13 +34329,13 @@
         </is>
       </c>
       <c r="V337" t="n">
-        <v>13296.2</v>
+        <v>16201.8</v>
       </c>
       <c r="W337" t="n">
         <v>411.4</v>
       </c>
       <c r="X337" t="n">
-        <v>-691.4</v>
+        <v>-1023.5</v>
       </c>
       <c r="Y337" t="inlineStr">
         <is>
@@ -34390,7 +34384,7 @@
         <v>1.1</v>
       </c>
       <c r="G338" t="n">
-        <v>11.1</v>
+        <v>10.95</v>
       </c>
       <c r="H338" t="n">
         <v>10015.7</v>
@@ -34496,7 +34490,7 @@
         <v>0.5</v>
       </c>
       <c r="G339" t="n">
-        <v>3.67</v>
+        <v>3.91</v>
       </c>
       <c r="H339" t="n">
         <v>3157.4</v>
@@ -34593,22 +34587,22 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>18.5</v>
+        <v>26.3</v>
       </c>
       <c r="E340" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F340" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G340" t="n">
-        <v>11.74</v>
+        <v>11.84</v>
       </c>
       <c r="H340" t="n">
         <v>6450</v>
       </c>
       <c r="I340" t="n">
-        <v>-2329.2</v>
+        <v>-288.9</v>
       </c>
       <c r="J340" t="n">
         <v>23.5</v>
@@ -34653,13 +34647,13 @@
         </is>
       </c>
       <c r="V340" t="n">
-        <v>11810.4</v>
+        <v>12776.5</v>
       </c>
       <c r="W340" t="n">
         <v>2500</v>
       </c>
       <c r="X340" t="n">
-        <v>-981.7</v>
+        <v>-201.2</v>
       </c>
       <c r="Y340" t="inlineStr">
         <is>
@@ -34699,22 +34693,22 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>22.4</v>
+        <v>25.4</v>
       </c>
       <c r="E341" t="n">
         <v>0.8</v>
       </c>
       <c r="F341" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G341" t="n">
-        <v>4.73</v>
+        <v>4.42</v>
       </c>
       <c r="H341" t="n">
         <v>6591</v>
       </c>
       <c r="I341" t="n">
-        <v>-627.2</v>
+        <v>-261.5</v>
       </c>
       <c r="J341" t="n">
         <v>19.1</v>
@@ -34811,7 +34805,7 @@
         <v>1.6</v>
       </c>
       <c r="G342" t="n">
-        <v>7.08</v>
+        <v>6.2</v>
       </c>
       <c r="H342" t="n">
         <v>13533</v>
@@ -34917,7 +34911,7 @@
         <v>3.3</v>
       </c>
       <c r="G343" t="n">
-        <v>53.86</v>
+        <v>53.92</v>
       </c>
       <c r="H343" t="n">
         <v>20371</v>
@@ -35014,22 +35008,22 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="E344" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F344" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G344" t="n">
-        <v>5.97</v>
+        <v>5.46</v>
       </c>
       <c r="H344" t="n">
         <v>7691</v>
       </c>
       <c r="I344" t="n">
-        <v>2700</v>
+        <v>2681.8</v>
       </c>
       <c r="J344" t="n">
         <v>20.5</v>
@@ -35129,7 +35123,7 @@
         <v>0.8</v>
       </c>
       <c r="G345" t="n">
-        <v>6.31</v>
+        <v>5.8</v>
       </c>
       <c r="H345" t="n">
         <v>12761.1</v>
@@ -35320,7 +35314,7 @@
         <v>0.7</v>
       </c>
       <c r="G347" t="n">
-        <v>9.119999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H347" t="n">
         <v>8506.700000000001</v>
@@ -35426,7 +35420,7 @@
         <v>1.7</v>
       </c>
       <c r="G348" t="n">
-        <v>3.41</v>
+        <v>4.38</v>
       </c>
       <c r="H348" t="n">
         <v>10913.6</v>
@@ -35614,7 +35608,7 @@
         <v>1.1</v>
       </c>
       <c r="G350" t="n">
-        <v>10.17</v>
+        <v>10.09</v>
       </c>
       <c r="H350" t="n">
         <v>2811.6</v>
@@ -35723,7 +35717,7 @@
         <v>6.1</v>
       </c>
       <c r="G351" t="n">
-        <v>8.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H351" t="n">
         <v>3332</v>
@@ -35820,22 +35814,22 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="E352" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F352" t="n">
         <v>0.9</v>
       </c>
       <c r="G352" t="n">
-        <v>11.78</v>
+        <v>12.08</v>
       </c>
       <c r="H352" t="n">
         <v>1578.4</v>
       </c>
       <c r="I352" t="n">
-        <v>171.8</v>
+        <v>221.3</v>
       </c>
       <c r="J352" t="n">
         <v>44.9</v>
@@ -35938,7 +35932,7 @@
         <v>0.6</v>
       </c>
       <c r="G353" t="n">
-        <v>7.21</v>
+        <v>7.13</v>
       </c>
       <c r="H353" t="n">
         <v>1797.1</v>
@@ -36035,22 +36029,22 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>23.8</v>
+        <v>19</v>
       </c>
       <c r="E354" t="n">
         <v>0.5</v>
       </c>
       <c r="F354" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G354" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="H354" t="n">
         <v>873.3</v>
       </c>
       <c r="I354" t="n">
-        <v>705.5</v>
+        <v>693.3</v>
       </c>
       <c r="J354" t="n">
         <v>49.9</v>
@@ -36150,7 +36144,7 @@
         <v>0.7</v>
       </c>
       <c r="G355" t="n">
-        <v>18.18</v>
+        <v>18.37</v>
       </c>
       <c r="H355" t="n">
         <v>6739.2</v>
@@ -36359,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>6.77</v>
+        <v>6.87</v>
       </c>
       <c r="H357" t="n">
         <v>238050</v>
@@ -36444,19 +36438,19 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F358" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G358" t="n">
-        <v>1.84</v>
+        <v>3.14</v>
       </c>
       <c r="H358" t="n">
         <v>5754.6</v>
       </c>
       <c r="I358" t="n">
-        <v>-506.6</v>
+        <v>-194.3</v>
       </c>
       <c r="J358" t="n">
         <v>31.8</v>
@@ -36559,7 +36553,7 @@
         <v>0.9</v>
       </c>
       <c r="G359" t="n">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="H359" t="n">
         <v>3887.9</v>
@@ -36665,7 +36659,7 @@
         <v>4.5</v>
       </c>
       <c r="G360" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H360" t="n">
         <v>3846.1</v>
@@ -36768,7 +36762,7 @@
         <v>28.5</v>
       </c>
       <c r="G361" t="n">
-        <v>11.61</v>
+        <v>10.9</v>
       </c>
       <c r="H361" t="n">
         <v>33240</v>
@@ -36971,7 +36965,7 @@
         <v>0.4</v>
       </c>
       <c r="G363" t="n">
-        <v>3.41</v>
+        <v>3.66</v>
       </c>
       <c r="H363" t="n">
         <v>4628</v>
@@ -37063,17 +37057,20 @@
           <t>Lider Turizm Hisse Senedi</t>
         </is>
       </c>
+      <c r="C364" t="n">
+        <v>15.2</v>
+      </c>
       <c r="E364" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="G364" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H364" t="n">
         <v>98175</v>
       </c>
       <c r="I364" t="n">
-        <v>-7842.7</v>
+        <v>-15126.1</v>
       </c>
       <c r="J364" t="n">
         <v>30.9</v>
@@ -37094,13 +37091,13 @@
         <v>-0.91</v>
       </c>
       <c r="P364" t="n">
-        <v>70</v>
+        <v>70.75</v>
       </c>
       <c r="Q364" t="n">
         <v>150.1</v>
       </c>
       <c r="R364" t="n">
-        <v>80.09999999999999</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="S364" t="inlineStr">
         <is>
@@ -37170,7 +37167,7 @@
         <v>1.3</v>
       </c>
       <c r="G365" t="n">
-        <v>15.97</v>
+        <v>16.26</v>
       </c>
       <c r="H365" t="n">
         <v>3614.8</v>
@@ -37336,25 +37333,25 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="D367" t="n">
-        <v>13.8</v>
+        <v>8.6</v>
       </c>
       <c r="E367" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="F367" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G367" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="H367" t="n">
         <v>4797.6</v>
       </c>
       <c r="I367" t="n">
-        <v>-655.2</v>
+        <v>-645.4</v>
       </c>
       <c r="J367" t="n">
         <v>63.4</v>
@@ -37457,7 +37454,7 @@
         <v>1.3</v>
       </c>
       <c r="G368" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="H368" t="n">
         <v>3265.9</v>
@@ -37554,25 +37551,25 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="D369" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E369" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F369" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G369" t="n">
-        <v>9.859999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="H369" t="n">
         <v>19253.5</v>
       </c>
       <c r="I369" t="n">
-        <v>-2292.1</v>
+        <v>-2319</v>
       </c>
       <c r="J369" t="n">
         <v>26.8</v>
@@ -37617,13 +37614,13 @@
         </is>
       </c>
       <c r="V369" t="n">
-        <v>7575.5</v>
+        <v>8353</v>
       </c>
       <c r="W369" t="n">
         <v>516.2</v>
       </c>
       <c r="X369" t="n">
-        <v>2023.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y369" t="inlineStr">
         <is>
@@ -37751,7 +37748,7 @@
         <v>0.4</v>
       </c>
       <c r="G371" t="n">
-        <v>5.43</v>
+        <v>5.01</v>
       </c>
       <c r="H371" t="n">
         <v>2833.9</v>
@@ -37781,10 +37778,10 @@
         <v>3.33</v>
       </c>
       <c r="Q371" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="R371" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
@@ -37848,19 +37845,19 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F372" t="n">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="G372" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="H372" t="n">
         <v>2914.8</v>
       </c>
       <c r="I372" t="n">
-        <v>30.7</v>
+        <v>39.4</v>
       </c>
       <c r="J372" t="n">
         <v>17</v>
@@ -37954,7 +37951,7 @@
         <v>6.1</v>
       </c>
       <c r="G373" t="n">
-        <v>1.07</v>
+        <v>5.03</v>
       </c>
       <c r="H373" t="n">
         <v>5613.3</v>
@@ -38051,7 +38048,7 @@
         <v>10.7</v>
       </c>
       <c r="G374" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="H374" t="n">
         <v>69095.89999999999</v>
@@ -38154,7 +38151,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G375" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="H375" t="n">
         <v>30261.8</v>
@@ -38254,7 +38251,7 @@
         <v>1.8</v>
       </c>
       <c r="G376" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="H376" t="n">
         <v>9746</v>
@@ -38363,7 +38360,7 @@
         <v>3.8</v>
       </c>
       <c r="G377" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="H377" t="n">
         <v>4142</v>
@@ -38459,7 +38456,7 @@
         <v>14.6</v>
       </c>
       <c r="G378" t="n">
-        <v>15.86</v>
+        <v>16.02</v>
       </c>
       <c r="H378" t="n">
         <v>188947.5</v>
@@ -38556,22 +38553,22 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>12.3</v>
+        <v>10.5</v>
       </c>
       <c r="E379" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F379" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G379" t="n">
-        <v>3.55</v>
+        <v>3.96</v>
       </c>
       <c r="H379" t="n">
         <v>2066.4</v>
       </c>
       <c r="I379" t="n">
-        <v>58.3</v>
+        <v>145.5</v>
       </c>
       <c r="J379" t="n">
         <v>38</v>
@@ -38671,7 +38668,7 @@
         <v>2.7</v>
       </c>
       <c r="G380" t="n">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="H380" t="n">
         <v>2724</v>
@@ -38701,10 +38698,10 @@
         <v>12.2</v>
       </c>
       <c r="Q380" t="n">
-        <v>17.3</v>
+        <v>17.27</v>
       </c>
       <c r="R380" t="n">
-        <v>5.1</v>
+        <v>5.07</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -38774,7 +38771,7 @@
         <v>20.6</v>
       </c>
       <c r="G381" t="n">
-        <v>0.37</v>
+        <v>1.68</v>
       </c>
       <c r="H381" t="n">
         <v>9984.6</v>
@@ -38801,13 +38798,13 @@
         <v>8.99</v>
       </c>
       <c r="P381" t="n">
-        <v>9.630000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="Q381" t="n">
         <v>30.16</v>
       </c>
       <c r="R381" t="n">
-        <v>20.53</v>
+        <v>20.11</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -38983,7 +38980,7 @@
         <v>6.7</v>
       </c>
       <c r="G383" t="n">
-        <v>0.59</v>
+        <v>1.23</v>
       </c>
       <c r="H383" t="n">
         <v>1231.1</v>
@@ -39101,7 +39098,7 @@
         <v>4.7</v>
       </c>
       <c r="G385" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="H385" t="n">
         <v>3270</v>
@@ -39295,7 +39292,7 @@
         <v>5.2</v>
       </c>
       <c r="G387" t="n">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="H387" t="n">
         <v>15047.5</v>
@@ -39394,7 +39391,7 @@
         <v>1.1</v>
       </c>
       <c r="G388" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="H388" t="n">
         <v>3553.3</v>
@@ -39605,7 +39602,7 @@
         <v>1.2</v>
       </c>
       <c r="G390" t="n">
-        <v>13.64</v>
+        <v>13.8</v>
       </c>
       <c r="H390" t="n">
         <v>21478.3</v>
@@ -39704,7 +39701,7 @@
         <v>1</v>
       </c>
       <c r="G391" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="H391" t="n">
         <v>3272</v>
@@ -39813,7 +39810,7 @@
         <v>0.3</v>
       </c>
       <c r="G392" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="H392" t="n">
         <v>1672.8</v>
@@ -39918,7 +39915,7 @@
         <v>1.8</v>
       </c>
       <c r="G393" t="n">
-        <v>10.4</v>
+        <v>7.98</v>
       </c>
       <c r="H393" t="n">
         <v>4530.8</v>
@@ -40027,7 +40024,7 @@
         <v>16.9</v>
       </c>
       <c r="G394" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="H394" t="n">
         <v>5503.4</v>
@@ -40124,25 +40121,25 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="D395" t="n">
-        <v>23.2</v>
+        <v>12.2</v>
       </c>
       <c r="E395" t="n">
         <v>0.9</v>
       </c>
       <c r="F395" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="G395" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="H395" t="n">
         <v>1779.8</v>
       </c>
       <c r="I395" t="n">
-        <v>164.5</v>
+        <v>271.9</v>
       </c>
       <c r="J395" t="n">
         <v>76.59999999999999</v>
@@ -40187,13 +40184,13 @@
         </is>
       </c>
       <c r="V395" t="n">
-        <v>1943.5</v>
+        <v>2007.2</v>
       </c>
       <c r="W395" t="n">
         <v>115.1</v>
       </c>
       <c r="X395" t="n">
-        <v>53.1</v>
+        <v>254.8</v>
       </c>
       <c r="Y395" t="inlineStr">
         <is>
@@ -40236,7 +40233,7 @@
         <v>0.9</v>
       </c>
       <c r="G396" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="H396" t="n">
         <v>3504.6</v>
@@ -40345,7 +40342,7 @@
         <v>4.6</v>
       </c>
       <c r="G397" t="n">
-        <v>6.82</v>
+        <v>4.88</v>
       </c>
       <c r="H397" t="n">
         <v>16425.6</v>
@@ -40530,7 +40527,7 @@
         <v>0.5</v>
       </c>
       <c r="G399" t="n">
-        <v>7.98</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H399" t="n">
         <v>4589.9</v>
@@ -40632,7 +40629,7 @@
         <v>7.3</v>
       </c>
       <c r="G400" t="n">
-        <v>5.7</v>
+        <v>5.58</v>
       </c>
       <c r="H400" t="n">
         <v>19740.2</v>
@@ -40835,7 +40832,7 @@
         <v>0.6</v>
       </c>
       <c r="G402" t="n">
-        <v>7.2</v>
+        <v>7.11</v>
       </c>
       <c r="H402" t="n">
         <v>3493.9</v>
@@ -40941,7 +40938,7 @@
         <v>0.4</v>
       </c>
       <c r="G403" t="n">
-        <v>83.17</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="H403" t="n">
         <v>6304.7</v>
@@ -41050,7 +41047,7 @@
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
       <c r="H404" t="n">
         <v>13581.3</v>
@@ -41162,13 +41159,13 @@
         <v>4</v>
       </c>
       <c r="P405" t="n">
-        <v>8.77</v>
+        <v>8.85</v>
       </c>
       <c r="Q405" t="n">
         <v>15.71</v>
       </c>
       <c r="R405" t="n">
-        <v>6.94</v>
+        <v>6.86</v>
       </c>
       <c r="S405" t="inlineStr">
         <is>
@@ -41241,7 +41238,7 @@
         <v>0.6</v>
       </c>
       <c r="G406" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H406" t="n">
         <v>10783.5</v>
@@ -41429,7 +41426,7 @@
         <v>0.4</v>
       </c>
       <c r="G408" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="H408" t="n">
         <v>4464.3</v>
@@ -41526,22 +41523,22 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>24.2</v>
+        <v>20.2</v>
       </c>
       <c r="E409" t="n">
-        <v>18.9</v>
+        <v>14.6</v>
       </c>
       <c r="F409" t="n">
         <v>3.9</v>
       </c>
       <c r="G409" t="n">
-        <v>79.31999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="H409" t="n">
         <v>16656.1</v>
       </c>
       <c r="I409" t="n">
-        <v>320</v>
+        <v>334.7</v>
       </c>
       <c r="J409" t="n">
         <v>6.4</v>
@@ -41635,13 +41632,13 @@
         <v>0.7</v>
       </c>
       <c r="G410" t="n">
-        <v>1.42</v>
+        <v>0.99</v>
       </c>
       <c r="H410" t="n">
         <v>3556.1</v>
       </c>
       <c r="I410" t="n">
-        <v>-143.3</v>
+        <v>-249.4</v>
       </c>
       <c r="J410" t="n">
         <v>30.2</v>
@@ -41744,7 +41741,7 @@
         <v>1.7</v>
       </c>
       <c r="G411" t="n">
-        <v>5.55</v>
+        <v>5.78</v>
       </c>
       <c r="H411" t="n">
         <v>2399.9</v>
@@ -41836,14 +41833,17 @@
           <t>Metro YO Hisse Senedi</t>
         </is>
       </c>
+      <c r="C412" t="n">
+        <v>4.3</v>
+      </c>
       <c r="E412" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H412" t="n">
         <v>398.6</v>
       </c>
       <c r="I412" t="n">
-        <v>-455.4</v>
+        <v>-584.8</v>
       </c>
       <c r="J412" t="n">
         <v>95</v>
@@ -42043,7 +42043,7 @@
         <v>6.2</v>
       </c>
       <c r="G414" t="n">
-        <v>1.07</v>
+        <v>0.9</v>
       </c>
       <c r="H414" t="n">
         <v>5791.5</v>
@@ -42146,7 +42146,7 @@
         <v>0.6</v>
       </c>
       <c r="G415" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H415" t="n">
         <v>4238.9</v>
@@ -42255,7 +42255,7 @@
         <v>10.5</v>
       </c>
       <c r="G416" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="H416" t="n">
         <v>17905.9</v>
@@ -42349,19 +42349,19 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F417" t="n">
-        <v>18.1</v>
+        <v>15.4</v>
       </c>
       <c r="G417" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="H417" t="n">
         <v>1911.6</v>
       </c>
       <c r="I417" t="n">
-        <v>-16.3</v>
+        <v>-9.1</v>
       </c>
       <c r="J417" t="n">
         <v>82.59999999999999</v>
@@ -42464,7 +42464,7 @@
         <v>1.1</v>
       </c>
       <c r="G418" t="n">
-        <v>11.07</v>
+        <v>11.23</v>
       </c>
       <c r="H418" t="n">
         <v>8625</v>
@@ -42567,7 +42567,7 @@
         <v>0.3</v>
       </c>
       <c r="G419" t="n">
-        <v>5.34</v>
+        <v>5.29</v>
       </c>
       <c r="H419" t="n">
         <v>19170</v>
@@ -42667,7 +42667,7 @@
         <v>0.5</v>
       </c>
       <c r="G420" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="H420" t="n">
         <v>3289.8</v>
@@ -42773,7 +42773,7 @@
         <v>1.7</v>
       </c>
       <c r="G421" t="n">
-        <v>21</v>
+        <v>21.02</v>
       </c>
       <c r="H421" t="n">
         <v>37192.9</v>
@@ -42982,7 +42982,7 @@
         <v>2.2</v>
       </c>
       <c r="G423" t="n">
-        <v>7.08</v>
+        <v>6.13</v>
       </c>
       <c r="H423" t="n">
         <v>1771.8</v>
@@ -43091,7 +43091,7 @@
         <v>1.1</v>
       </c>
       <c r="G424" t="n">
-        <v>9.119999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H424" t="n">
         <v>9604</v>
@@ -43188,7 +43188,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>6.15</v>
+        <v>6.04</v>
       </c>
       <c r="H425" t="n">
         <v>125859.5</v>
@@ -43297,7 +43297,7 @@
         <v>0.7</v>
       </c>
       <c r="G426" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="H426" t="n">
         <v>8299.700000000001</v>
@@ -43403,7 +43403,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G427" t="n">
-        <v>18.84</v>
+        <v>19.12</v>
       </c>
       <c r="H427" t="n">
         <v>6523</v>
@@ -43506,7 +43506,7 @@
         <v>3.6</v>
       </c>
       <c r="G428" t="n">
-        <v>3.37</v>
+        <v>3.16</v>
       </c>
       <c r="H428" t="n">
         <v>3785.5</v>
@@ -43603,13 +43603,13 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>12.3</v>
+        <v>15.9</v>
       </c>
       <c r="E429" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F429" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G429" t="n">
         <v>3.01</v>
@@ -43618,7 +43618,7 @@
         <v>940.8</v>
       </c>
       <c r="I429" t="n">
-        <v>504.2</v>
+        <v>432</v>
       </c>
       <c r="J429" t="n">
         <v>62.9</v>
@@ -43721,7 +43721,7 @@
         <v>1.9</v>
       </c>
       <c r="G430" t="n">
-        <v>26.02</v>
+        <v>26.18</v>
       </c>
       <c r="H430" t="n">
         <v>6840</v>
@@ -43933,7 +43933,7 @@
         <v>0.1</v>
       </c>
       <c r="G432" t="n">
-        <v>7.71</v>
+        <v>7.81</v>
       </c>
       <c r="H432" t="n">
         <v>3034.7</v>
@@ -44036,7 +44036,7 @@
         <v>4</v>
       </c>
       <c r="G433" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="H433" t="n">
         <v>1675.6</v>
@@ -44142,7 +44142,7 @@
         <v>1.4</v>
       </c>
       <c r="G434" t="n">
-        <v>11.78</v>
+        <v>11.6</v>
       </c>
       <c r="H434" t="n">
         <v>45930</v>
@@ -44245,7 +44245,7 @@
         <v>7.1</v>
       </c>
       <c r="G435" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H435" t="n">
         <v>2317.4</v>
@@ -44275,10 +44275,10 @@
         <v>302.5</v>
       </c>
       <c r="Q435" t="n">
-        <v>365</v>
+        <v>357.25</v>
       </c>
       <c r="R435" t="n">
-        <v>62.5</v>
+        <v>54.75</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -44427,22 +44427,22 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>19.5</v>
+        <v>16.2</v>
       </c>
       <c r="E437" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="F437" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="G437" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="H437" t="n">
         <v>1033</v>
       </c>
       <c r="I437" t="n">
-        <v>-154.5</v>
+        <v>-153.3</v>
       </c>
       <c r="J437" t="n">
         <v>52.7</v>
@@ -44533,22 +44533,22 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>13.7</v>
+        <v>17.5</v>
       </c>
       <c r="E438" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F438" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G438" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="H438" t="n">
         <v>714</v>
       </c>
       <c r="I438" t="n">
-        <v>-62.6</v>
+        <v>-31.3</v>
       </c>
       <c r="J438" t="n">
         <v>77.90000000000001</v>
@@ -44639,13 +44639,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="D439" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E439" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F439" t="n">
         <v>0.2</v>
@@ -44657,7 +44657,7 @@
         <v>17100</v>
       </c>
       <c r="I439" t="n">
-        <v>-10738.1</v>
+        <v>-11914.4</v>
       </c>
       <c r="J439" t="n">
         <v>30.3</v>
@@ -44754,7 +44754,7 @@
         <v>11.4</v>
       </c>
       <c r="G440" t="n">
-        <v>12.92</v>
+        <v>5.96</v>
       </c>
       <c r="H440" t="n">
         <v>26631.4</v>
@@ -44854,7 +44854,7 @@
         <v>0.4</v>
       </c>
       <c r="G441" t="n">
-        <v>10.55</v>
+        <v>10.9</v>
       </c>
       <c r="H441" t="n">
         <v>2190</v>
@@ -44946,7 +44946,7 @@
         <v>0.3</v>
       </c>
       <c r="G442" t="n">
-        <v>8.81</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H442" t="n">
         <v>17806.9</v>
@@ -45049,7 +45049,7 @@
         <v>4.6</v>
       </c>
       <c r="G443" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="H443" t="n">
         <v>2619.5</v>
@@ -45158,7 +45158,7 @@
         <v>1.4</v>
       </c>
       <c r="G444" t="n">
-        <v>6.76</v>
+        <v>5.17</v>
       </c>
       <c r="H444" t="n">
         <v>3230.4</v>
@@ -45264,7 +45264,7 @@
         <v>0.8</v>
       </c>
       <c r="G445" t="n">
-        <v>10.03</v>
+        <v>10.43</v>
       </c>
       <c r="H445" t="n">
         <v>4760.1</v>
@@ -45464,19 +45464,19 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>6.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E447" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G447" t="n">
-        <v>8.470000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H447" t="n">
         <v>31400</v>
       </c>
       <c r="I447" t="n">
-        <v>-1231.3</v>
+        <v>2.4</v>
       </c>
       <c r="J447" t="n">
         <v>20</v>
@@ -45500,10 +45500,10 @@
         <v>1.45</v>
       </c>
       <c r="Q447" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R447" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -45521,13 +45521,13 @@
         </is>
       </c>
       <c r="V447" t="n">
-        <v>39782.8</v>
+        <v>43272.6</v>
       </c>
       <c r="W447" t="n">
         <v>20000</v>
       </c>
       <c r="X447" t="n">
-        <v>4566</v>
+        <v>-504.1</v>
       </c>
       <c r="Y447" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>34.8</v>
       </c>
       <c r="G448" t="n">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="H448" t="n">
         <v>2770.6</v>
@@ -45676,7 +45676,7 @@
         <v>23.3</v>
       </c>
       <c r="G449" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H449" t="n">
         <v>3361.9</v>
@@ -45776,16 +45776,16 @@
         <v>0.5</v>
       </c>
       <c r="F450" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G450" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="H450" t="n">
         <v>7233.8</v>
       </c>
       <c r="I450" t="n">
-        <v>5372.7</v>
+        <v>6157</v>
       </c>
       <c r="J450" t="n">
         <v>28.5</v>
@@ -45882,7 +45882,7 @@
         <v>36.5</v>
       </c>
       <c r="G451" t="n">
-        <v>11.52</v>
+        <v>11.14</v>
       </c>
       <c r="H451" t="n">
         <v>88704</v>
@@ -45975,22 +45975,22 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>12.6</v>
+        <v>27.2</v>
       </c>
       <c r="E452" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="F452" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G452" t="n">
-        <v>5.16</v>
+        <v>5.08</v>
       </c>
       <c r="H452" t="n">
         <v>14632.6</v>
       </c>
       <c r="I452" t="n">
-        <v>-3740.6</v>
+        <v>-3622.7</v>
       </c>
       <c r="J452" t="n">
         <v>43.4</v>
@@ -46035,13 +46035,13 @@
         </is>
       </c>
       <c r="V452" t="n">
-        <v>4244.6</v>
+        <v>3963.7</v>
       </c>
       <c r="W452" t="n">
-        <v>600</v>
+        <v>674.9</v>
       </c>
       <c r="X452" t="n">
-        <v>1165.8</v>
+        <v>-704.3</v>
       </c>
       <c r="Y452" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>0.3</v>
       </c>
       <c r="G453" t="n">
-        <v>5.4</v>
+        <v>6.03</v>
       </c>
       <c r="H453" t="n">
         <v>3453.5</v>
@@ -46189,7 +46189,7 @@
         <v>13.7</v>
       </c>
       <c r="G454" t="n">
-        <v>9.43</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H454" t="n">
         <v>81950</v>
@@ -46292,7 +46292,7 @@
         <v>1.1</v>
       </c>
       <c r="G455" t="n">
-        <v>0.87</v>
+        <v>0.39</v>
       </c>
       <c r="H455" t="n">
         <v>2434.3</v>
@@ -46568,25 +46568,25 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>19.9</v>
+        <v>16.3</v>
       </c>
       <c r="D458" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="E458" t="n">
         <v>0.4</v>
       </c>
       <c r="F458" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G458" t="n">
-        <v>7.9</v>
+        <v>7.94</v>
       </c>
       <c r="H458" t="n">
         <v>3740.2</v>
       </c>
       <c r="I458" t="n">
-        <v>3554.5</v>
+        <v>3699.9</v>
       </c>
       <c r="J458" t="n">
         <v>33.1</v>
@@ -46771,7 +46771,7 @@
         <v>1.4</v>
       </c>
       <c r="G460" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="H460" t="n">
         <v>3337.5</v>
@@ -46867,23 +46867,26 @@
           <t>Plastikkart A.Ş Hisse Senedi</t>
         </is>
       </c>
+      <c r="C461" t="n">
+        <v>32.7</v>
+      </c>
       <c r="D461" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E461" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="F461" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="G461" t="n">
-        <v>33.43</v>
+        <v>34.87</v>
       </c>
       <c r="H461" t="n">
         <v>3109.9</v>
       </c>
       <c r="I461" t="n">
-        <v>-73</v>
+        <v>-62.2</v>
       </c>
       <c r="J461" t="n">
         <v>33.7</v>
@@ -46974,25 +46977,25 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>21.6</v>
+        <v>26.7</v>
       </c>
       <c r="D462" t="n">
-        <v>16.3</v>
+        <v>22.7</v>
       </c>
       <c r="E462" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="F462" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G462" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H462" t="n">
         <v>3856.9</v>
       </c>
       <c r="I462" t="n">
-        <v>-471</v>
+        <v>-601.8</v>
       </c>
       <c r="J462" t="n">
         <v>32.6</v>
@@ -47095,7 +47098,7 @@
         <v>1.2</v>
       </c>
       <c r="G463" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="H463" t="n">
         <v>6559.3</v>
@@ -47204,7 +47207,7 @@
         <v>1</v>
       </c>
       <c r="G464" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="H464" t="n">
         <v>3384</v>
@@ -47231,13 +47234,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="P464" t="n">
-        <v>40.88</v>
+        <v>41.9</v>
       </c>
       <c r="Q464" t="n">
         <v>54.45</v>
       </c>
       <c r="R464" t="n">
-        <v>13.57</v>
+        <v>12.55</v>
       </c>
       <c r="S464" t="inlineStr">
         <is>
@@ -47297,22 +47300,22 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>21.1</v>
+        <v>24.8</v>
       </c>
       <c r="E465" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F465" t="n">
         <v>0.6</v>
       </c>
       <c r="G465" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="H465" t="n">
         <v>4015</v>
       </c>
       <c r="I465" t="n">
-        <v>5643.2</v>
+        <v>6051.4</v>
       </c>
       <c r="J465" t="n">
         <v>37.7</v>
@@ -47336,10 +47339,10 @@
         <v>10.48</v>
       </c>
       <c r="Q465" t="n">
-        <v>14.25</v>
+        <v>13.36</v>
       </c>
       <c r="R465" t="n">
-        <v>3.77</v>
+        <v>2.88</v>
       </c>
       <c r="S465" t="inlineStr">
         <is>
@@ -47357,13 +47360,13 @@
         </is>
       </c>
       <c r="V465" t="n">
-        <v>10948.5</v>
+        <v>11759.8</v>
       </c>
       <c r="W465" t="n">
         <v>314.7</v>
       </c>
       <c r="X465" t="n">
-        <v>-941.7</v>
+        <v>49.5</v>
       </c>
       <c r="Y465" t="inlineStr">
         <is>
@@ -47406,7 +47409,7 @@
         <v>1.2</v>
       </c>
       <c r="G466" t="n">
-        <v>11.06</v>
+        <v>10.82</v>
       </c>
       <c r="H466" t="n">
         <v>16140.9</v>
@@ -47506,7 +47509,7 @@
         <v>18.8</v>
       </c>
       <c r="G467" t="n">
-        <v>27.16</v>
+        <v>27.19</v>
       </c>
       <c r="H467" t="n">
         <v>20081.3</v>
@@ -47608,7 +47611,7 @@
         <v>36.7</v>
       </c>
       <c r="G468" t="n">
-        <v>4.76</v>
+        <v>4.38</v>
       </c>
       <c r="H468" t="n">
         <v>1540.6</v>
@@ -47714,7 +47717,7 @@
         <v>0.5</v>
       </c>
       <c r="G469" t="n">
-        <v>3.97</v>
+        <v>3.2</v>
       </c>
       <c r="H469" t="n">
         <v>8287.9</v>
@@ -47820,7 +47823,7 @@
         <v>4.6</v>
       </c>
       <c r="G470" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="H470" t="n">
         <v>2855.3</v>
@@ -47850,10 +47853,10 @@
         <v>17.46</v>
       </c>
       <c r="Q470" t="n">
-        <v>21.94</v>
+        <v>21.44</v>
       </c>
       <c r="R470" t="n">
-        <v>4.48</v>
+        <v>3.98</v>
       </c>
       <c r="S470" t="inlineStr">
         <is>
@@ -47917,10 +47920,10 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="F471" t="n">
-        <v>20.8</v>
+        <v>18.3</v>
       </c>
       <c r="G471" t="n">
         <v>2.25</v>
@@ -47929,7 +47932,7 @@
         <v>2275.5</v>
       </c>
       <c r="I471" t="n">
-        <v>24.1</v>
+        <v>17.9</v>
       </c>
       <c r="J471" t="n">
         <v>71.59999999999999</v>
@@ -48020,22 +48023,22 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>19.1</v>
+        <v>22.9</v>
       </c>
       <c r="E472" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="F472" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="G472" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H472" t="n">
         <v>1039.5</v>
       </c>
       <c r="I472" t="n">
-        <v>-349</v>
+        <v>-424.4</v>
       </c>
       <c r="J472" t="n">
         <v>73.59999999999999</v>
@@ -48132,7 +48135,7 @@
         <v>0.6</v>
       </c>
       <c r="G473" t="n">
-        <v>6.56</v>
+        <v>7.31</v>
       </c>
       <c r="H473" t="n">
         <v>20702.5</v>
@@ -48426,7 +48429,7 @@
         <v>1.4</v>
       </c>
       <c r="G476" t="n">
-        <v>7.84</v>
+        <v>7.26</v>
       </c>
       <c r="H476" t="n">
         <v>9820.799999999999</v>
@@ -48453,13 +48456,13 @@
         <v>8.73</v>
       </c>
       <c r="P476" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="Q476" t="n">
         <v>4.17</v>
       </c>
       <c r="R476" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S476" t="inlineStr">
         <is>
@@ -48529,7 +48532,7 @@
         <v>17.9</v>
       </c>
       <c r="G477" t="n">
-        <v>13.81</v>
+        <v>13.96</v>
       </c>
       <c r="H477" t="n">
         <v>112054.5</v>
@@ -48628,7 +48631,7 @@
         <v>3.4</v>
       </c>
       <c r="G478" t="n">
-        <v>86</v>
+        <v>85.86</v>
       </c>
       <c r="H478" t="n">
         <v>32173.7</v>
@@ -49009,7 +49012,7 @@
         <v>9.1</v>
       </c>
       <c r="G482" t="n">
-        <v>1.69</v>
+        <v>2.01</v>
       </c>
       <c r="H482" t="n">
         <v>806.6</v>
@@ -49112,7 +49115,7 @@
         <v>6.1</v>
       </c>
       <c r="G483" t="n">
-        <v>9.300000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="H483" t="n">
         <v>1660</v>
@@ -49205,22 +49208,22 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>8.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="E484" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F484" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G484" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="H484" t="n">
         <v>2681.4</v>
       </c>
       <c r="I484" t="n">
-        <v>612.6</v>
+        <v>410.1</v>
       </c>
       <c r="J484" t="n">
         <v>41.1</v>
@@ -49317,7 +49320,7 @@
         <v>11.7</v>
       </c>
       <c r="G485" t="n">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="H485" t="n">
         <v>3652</v>
@@ -49416,7 +49419,7 @@
         <v>0.7</v>
       </c>
       <c r="G486" t="n">
-        <v>42.04</v>
+        <v>42.1</v>
       </c>
       <c r="H486" t="n">
         <v>60600</v>
@@ -49443,13 +49446,13 @@
         <v>0.01</v>
       </c>
       <c r="P486" t="n">
-        <v>28.34</v>
+        <v>28.54</v>
       </c>
       <c r="Q486" t="n">
         <v>35.98</v>
       </c>
       <c r="R486" t="n">
-        <v>7.64</v>
+        <v>7.44</v>
       </c>
       <c r="S486" t="inlineStr">
         <is>
@@ -49525,7 +49528,7 @@
         <v>3.5</v>
       </c>
       <c r="G487" t="n">
-        <v>58.71</v>
+        <v>58.68</v>
       </c>
       <c r="H487" t="n">
         <v>40000</v>
@@ -49634,7 +49637,7 @@
         <v>2.7</v>
       </c>
       <c r="G488" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="H488" t="n">
         <v>4864</v>
@@ -49812,7 +49815,7 @@
         <v>14.4</v>
       </c>
       <c r="G490" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H490" t="n">
         <v>622.7</v>
@@ -50023,7 +50026,7 @@
         <v>2.8</v>
       </c>
       <c r="G492" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H492" t="n">
         <v>2816.3</v>
@@ -50120,19 +50123,19 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F493" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G493" t="n">
-        <v>4.97</v>
+        <v>5.14</v>
       </c>
       <c r="H493" t="n">
         <v>3798</v>
       </c>
       <c r="I493" t="n">
-        <v>-156</v>
+        <v>-105.7</v>
       </c>
       <c r="J493" t="n">
         <v>13.5</v>
@@ -50232,7 +50235,7 @@
         <v>0.5</v>
       </c>
       <c r="G494" t="n">
-        <v>6.95</v>
+        <v>7.01</v>
       </c>
       <c r="H494" t="n">
         <v>26460</v>
@@ -50262,10 +50265,10 @@
         <v>26</v>
       </c>
       <c r="Q494" t="n">
-        <v>45.98</v>
+        <v>43</v>
       </c>
       <c r="R494" t="n">
-        <v>19.98</v>
+        <v>17</v>
       </c>
       <c r="S494" t="inlineStr">
         <is>
@@ -50338,7 +50341,7 @@
         <v>4.9</v>
       </c>
       <c r="G495" t="n">
-        <v>22.24</v>
+        <v>21.98</v>
       </c>
       <c r="H495" t="n">
         <v>137581</v>
@@ -50447,7 +50450,7 @@
         <v>1.9</v>
       </c>
       <c r="G496" t="n">
-        <v>6.09</v>
+        <v>5.75</v>
       </c>
       <c r="H496" t="n">
         <v>3765.2</v>
@@ -50543,20 +50546,23 @@
           <t>SDT Uzay Hisse Senedi</t>
         </is>
       </c>
+      <c r="D497" t="n">
+        <v>30.7</v>
+      </c>
       <c r="E497" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="F497" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>7.36</v>
+        <v>7.63</v>
       </c>
       <c r="H497" t="n">
         <v>12748.4</v>
       </c>
       <c r="I497" t="n">
-        <v>141.5</v>
+        <v>424.1</v>
       </c>
       <c r="J497" t="n">
         <v>27.6</v>
@@ -50601,13 +50607,13 @@
         </is>
       </c>
       <c r="V497" t="n">
-        <v>2432.8</v>
+        <v>2690.5</v>
       </c>
       <c r="W497" t="n">
         <v>58</v>
       </c>
       <c r="X497" t="n">
-        <v>30.2</v>
+        <v>13.9</v>
       </c>
       <c r="Y497" t="inlineStr">
         <is>
@@ -50659,7 +50665,7 @@
         <v>3.4</v>
       </c>
       <c r="G498" t="n">
-        <v>11.77</v>
+        <v>11.33</v>
       </c>
       <c r="H498" t="n">
         <v>10149.3</v>
@@ -50686,13 +50692,13 @@
         <v>-1.26</v>
       </c>
       <c r="P498" t="n">
-        <v>38.5</v>
+        <v>46.08</v>
       </c>
       <c r="Q498" t="n">
         <v>67.65000000000001</v>
       </c>
       <c r="R498" t="n">
-        <v>29.15</v>
+        <v>21.57</v>
       </c>
       <c r="S498" t="inlineStr">
         <is>
@@ -50759,7 +50765,7 @@
         <v>0.6</v>
       </c>
       <c r="G499" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="H499" t="n">
         <v>4010.8</v>
@@ -50886,13 +50892,13 @@
         <v>0.36</v>
       </c>
       <c r="P500" t="n">
-        <v>9.15</v>
+        <v>9.32</v>
       </c>
       <c r="Q500" t="n">
         <v>11.35</v>
       </c>
       <c r="R500" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S500" t="inlineStr">
         <is>
@@ -50983,13 +50989,13 @@
         <v>-1.78</v>
       </c>
       <c r="P501" t="n">
-        <v>3.53</v>
+        <v>4.26</v>
       </c>
       <c r="Q501" t="n">
         <v>8.640000000000001</v>
       </c>
       <c r="R501" t="n">
-        <v>5.11</v>
+        <v>4.38</v>
       </c>
       <c r="S501" t="inlineStr">
         <is>
@@ -51147,7 +51153,7 @@
         <v>1.5</v>
       </c>
       <c r="G503" t="n">
-        <v>1.3</v>
+        <v>2.42</v>
       </c>
       <c r="H503" t="n">
         <v>2590.4</v>
@@ -51253,7 +51259,7 @@
         <v>3</v>
       </c>
       <c r="G504" t="n">
-        <v>3.1</v>
+        <v>2.17</v>
       </c>
       <c r="H504" t="n">
         <v>3601.4</v>
@@ -51356,7 +51362,7 @@
         <v>3.4</v>
       </c>
       <c r="G505" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="H505" t="n">
         <v>1066</v>
@@ -51462,7 +51468,7 @@
         <v>0.6</v>
       </c>
       <c r="G506" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="H506" t="n">
         <v>892.5</v>
@@ -51492,10 +51498,10 @@
         <v>2.33</v>
       </c>
       <c r="Q506" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R506" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="S506" t="inlineStr">
         <is>
@@ -51571,7 +51577,7 @@
         <v>1.2</v>
       </c>
       <c r="G507" t="n">
-        <v>12.01</v>
+        <v>11.88</v>
       </c>
       <c r="H507" t="n">
         <v>146605.4</v>
@@ -51674,7 +51680,7 @@
         <v>1.4</v>
       </c>
       <c r="G508" t="n">
-        <v>5.7</v>
+        <v>5.94</v>
       </c>
       <c r="H508" t="n">
         <v>30675</v>
@@ -51698,13 +51704,13 @@
         <v>-0.66</v>
       </c>
       <c r="P508" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="Q508" t="n">
         <v>13.25</v>
       </c>
       <c r="R508" t="n">
-        <v>4.47</v>
+        <v>4.35</v>
       </c>
       <c r="S508" t="inlineStr">
         <is>
@@ -51774,7 +51780,7 @@
         <v>1.4</v>
       </c>
       <c r="G509" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="H509" t="n">
         <v>1690</v>
@@ -51877,7 +51883,7 @@
         <v>14.1</v>
       </c>
       <c r="G510" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="H510" t="n">
         <v>3211</v>
@@ -51974,7 +51980,7 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E511" t="n">
         <v>1.8</v>
@@ -51983,13 +51989,13 @@
         <v>0.1</v>
       </c>
       <c r="G511" t="n">
-        <v>11.02</v>
+        <v>10.72</v>
       </c>
       <c r="H511" t="n">
         <v>2090.9</v>
       </c>
       <c r="I511" t="n">
-        <v>164.9</v>
+        <v>558.9</v>
       </c>
       <c r="J511" t="n">
         <v>33.8</v>
@@ -52034,13 +52040,13 @@
         </is>
       </c>
       <c r="V511" t="n">
-        <v>1148.9</v>
+        <v>1187.5</v>
       </c>
       <c r="W511" t="n">
         <v>155</v>
       </c>
       <c r="X511" t="n">
-        <v>-113.8</v>
+        <v>-76.8</v>
       </c>
       <c r="Y511" t="inlineStr">
         <is>
@@ -52089,7 +52095,7 @@
         <v>6.2</v>
       </c>
       <c r="G512" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="H512" t="n">
         <v>1150.2</v>
@@ -52191,7 +52197,7 @@
         <v>2.2</v>
       </c>
       <c r="G513" t="n">
-        <v>11.27</v>
+        <v>11.1</v>
       </c>
       <c r="H513" t="n">
         <v>13868.6</v>
@@ -52288,19 +52294,19 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>18.9</v>
+        <v>23.6</v>
       </c>
       <c r="D514" t="n">
         <v>0</v>
       </c>
       <c r="E514" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="F514" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="G514" t="n">
-        <v>7.13</v>
+        <v>8.9</v>
       </c>
       <c r="H514" t="n">
         <v>12876</v>
@@ -52388,7 +52394,7 @@
         <v>0.3</v>
       </c>
       <c r="G515" t="n">
-        <v>9.41</v>
+        <v>9.42</v>
       </c>
       <c r="H515" t="n">
         <v>14640</v>
@@ -52485,22 +52491,22 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>15</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E516" t="n">
         <v>0.5</v>
       </c>
       <c r="F516" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G516" t="n">
-        <v>6.76</v>
+        <v>6.67</v>
       </c>
       <c r="H516" t="n">
         <v>2430</v>
       </c>
       <c r="I516" t="n">
-        <v>1001</v>
+        <v>938</v>
       </c>
       <c r="J516" t="n">
         <v>53.6</v>
@@ -52591,10 +52597,10 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F517" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G517" t="n">
         <v>0</v>
@@ -52603,7 +52609,7 @@
         <v>8346</v>
       </c>
       <c r="I517" t="n">
-        <v>-52.9</v>
+        <v>-83.2</v>
       </c>
       <c r="J517" t="n">
         <v>4.1</v>
@@ -52727,10 +52733,10 @@
         <v>9</v>
       </c>
       <c r="Q518" t="n">
-        <v>12.61</v>
+        <v>12.38</v>
       </c>
       <c r="R518" t="n">
-        <v>3.61</v>
+        <v>3.38</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -52803,7 +52809,7 @@
         <v>0.9</v>
       </c>
       <c r="G519" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="H519" t="n">
         <v>7389.9</v>
@@ -52985,16 +52991,16 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G521" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="H521" t="n">
         <v>10278.6</v>
       </c>
       <c r="I521" t="n">
-        <v>-96.8</v>
+        <v>-137.3</v>
       </c>
       <c r="J521" t="n">
         <v>5.4</v>
@@ -53091,7 +53097,7 @@
         <v>0.4</v>
       </c>
       <c r="G522" t="n">
-        <v>22.3</v>
+        <v>22.55</v>
       </c>
       <c r="H522" t="n">
         <v>10855</v>
@@ -53303,7 +53309,7 @@
         <v>1.3</v>
       </c>
       <c r="G524" t="n">
-        <v>9.56</v>
+        <v>9.58</v>
       </c>
       <c r="H524" t="n">
         <v>16943.2</v>
@@ -53399,20 +53405,17 @@
           <t>Sur GYO Hisse Senedi</t>
         </is>
       </c>
-      <c r="C525" t="n">
-        <v>12.2</v>
-      </c>
       <c r="E525" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G525" t="n">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="H525" t="n">
         <v>11884.1</v>
       </c>
       <c r="I525" t="n">
-        <v>-39.7</v>
+        <v>-36.9</v>
       </c>
       <c r="J525" t="n">
         <v>26.9</v>
@@ -53433,13 +53436,13 @@
         <v>-1.67</v>
       </c>
       <c r="P525" t="n">
-        <v>47.8</v>
+        <v>51.5</v>
       </c>
       <c r="Q525" t="n">
         <v>77.45</v>
       </c>
       <c r="R525" t="n">
-        <v>29.65</v>
+        <v>25.95</v>
       </c>
       <c r="S525" t="inlineStr">
         <is>
@@ -53457,13 +53460,13 @@
         </is>
       </c>
       <c r="V525" t="n">
-        <v>9060.299999999999</v>
+        <v>9975.799999999999</v>
       </c>
       <c r="W525" t="n">
         <v>167.5</v>
       </c>
       <c r="X525" t="n">
-        <v>976.7</v>
+        <v>5.4</v>
       </c>
       <c r="Y525" t="inlineStr">
         <is>
@@ -53512,7 +53515,7 @@
         <v>1.1</v>
       </c>
       <c r="G526" t="n">
-        <v>12.84</v>
+        <v>12.83</v>
       </c>
       <c r="H526" t="n">
         <v>4816</v>
@@ -53612,7 +53615,7 @@
         <v>4.9</v>
       </c>
       <c r="G527" t="n">
-        <v>8.81</v>
+        <v>8.01</v>
       </c>
       <c r="H527" t="n">
         <v>20826.1</v>
@@ -53791,22 +53794,22 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>27.5</v>
+        <v>20.4</v>
       </c>
       <c r="E529" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F529" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G529" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="H529" t="n">
         <v>8583.799999999999</v>
       </c>
       <c r="I529" t="n">
-        <v>847.1</v>
+        <v>1223.8</v>
       </c>
       <c r="J529" t="n">
         <v>23.8</v>
@@ -53830,10 +53833,10 @@
         <v>359.5</v>
       </c>
       <c r="Q529" t="n">
-        <v>456.25</v>
+        <v>444.5</v>
       </c>
       <c r="R529" t="n">
-        <v>96.75</v>
+        <v>85</v>
       </c>
       <c r="S529" t="inlineStr">
         <is>
@@ -53906,7 +53909,7 @@
         <v>7.9</v>
       </c>
       <c r="G530" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="H530" t="n">
         <v>14316.7</v>
@@ -54015,7 +54018,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>14.04</v>
+        <v>13.57</v>
       </c>
       <c r="H531" t="n">
         <v>4401.5</v>
@@ -54209,7 +54212,7 @@
         <v>1.1</v>
       </c>
       <c r="G533" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="H533" t="n">
         <v>46247.7</v>
@@ -54403,7 +54406,7 @@
         <v>6.2</v>
       </c>
       <c r="G535" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="H535" t="n">
         <v>18071</v>
@@ -54499,8 +54502,11 @@
           <t>Trend GYO Hisse Senedi</t>
         </is>
       </c>
+      <c r="C536" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="E536" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="G536" t="n">
         <v>0.64</v>
@@ -54509,7 +54515,7 @@
         <v>1286.8</v>
       </c>
       <c r="I536" t="n">
-        <v>-123.3</v>
+        <v>-337.9</v>
       </c>
       <c r="J536" t="n">
         <v>89.8</v>
@@ -54533,10 +54539,10 @@
         <v>15.84</v>
       </c>
       <c r="Q536" t="n">
-        <v>32.28</v>
+        <v>29.08</v>
       </c>
       <c r="R536" t="n">
-        <v>16.44</v>
+        <v>13.24</v>
       </c>
       <c r="S536" t="inlineStr">
         <is>
@@ -54606,7 +54612,7 @@
         <v>6.5</v>
       </c>
       <c r="G537" t="n">
-        <v>6.32</v>
+        <v>6.35</v>
       </c>
       <c r="H537" t="n">
         <v>52291</v>
@@ -54709,7 +54715,7 @@
         <v>29.4</v>
       </c>
       <c r="G538" t="n">
-        <v>2.11</v>
+        <v>1.27</v>
       </c>
       <c r="H538" t="n">
         <v>3633</v>
@@ -54818,7 +54824,7 @@
         <v>0.3</v>
       </c>
       <c r="G539" t="n">
-        <v>11.76</v>
+        <v>11.24</v>
       </c>
       <c r="H539" t="n">
         <v>168700</v>
@@ -54845,13 +54851,13 @@
         <v>-0.08</v>
       </c>
       <c r="P539" t="n">
-        <v>207</v>
+        <v>211.9</v>
       </c>
       <c r="Q539" t="n">
         <v>396</v>
       </c>
       <c r="R539" t="n">
-        <v>189</v>
+        <v>184.1</v>
       </c>
       <c r="S539" t="inlineStr">
         <is>
@@ -54924,7 +54930,7 @@
         <v>1.5</v>
       </c>
       <c r="G540" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="H540" t="n">
         <v>9545</v>
@@ -54951,13 +54957,13 @@
         <v>2.8</v>
       </c>
       <c r="P540" t="n">
-        <v>12.84</v>
+        <v>13</v>
       </c>
       <c r="Q540" t="n">
         <v>19.18</v>
       </c>
       <c r="R540" t="n">
-        <v>6.34</v>
+        <v>6.18</v>
       </c>
       <c r="S540" t="inlineStr">
         <is>
@@ -55033,7 +55039,7 @@
         <v>10.4</v>
       </c>
       <c r="G541" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="H541" t="n">
         <v>2512.5</v>
@@ -55391,7 +55397,7 @@
         <v>2</v>
       </c>
       <c r="G545" t="n">
-        <v>7.99</v>
+        <v>7.98</v>
       </c>
       <c r="H545" t="n">
         <v>2001.3</v>
@@ -55490,7 +55496,7 @@
         <v>6</v>
       </c>
       <c r="G546" t="n">
-        <v>3.38</v>
+        <v>2.89</v>
       </c>
       <c r="H546" t="n">
         <v>6874.9</v>
@@ -55517,13 +55523,13 @@
         <v>-0.19</v>
       </c>
       <c r="P546" t="n">
-        <v>363.25</v>
+        <v>412</v>
       </c>
       <c r="Q546" t="n">
         <v>686.5</v>
       </c>
       <c r="R546" t="n">
-        <v>323.25</v>
+        <v>274.5</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -55596,7 +55602,7 @@
         <v>4.8</v>
       </c>
       <c r="G547" t="n">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="H547" t="n">
         <v>11718.5</v>
@@ -55705,7 +55711,7 @@
         <v>2.8</v>
       </c>
       <c r="G548" t="n">
-        <v>4.23</v>
+        <v>3.82</v>
       </c>
       <c r="H548" t="n">
         <v>10024</v>
@@ -55978,7 +55984,7 @@
         <v>0.8</v>
       </c>
       <c r="G551" t="n">
-        <v>3.61</v>
+        <v>3.69</v>
       </c>
       <c r="H551" t="n">
         <v>11829.2</v>
@@ -56087,7 +56093,7 @@
         <v>0.4</v>
       </c>
       <c r="G552" t="n">
-        <v>21.47</v>
+        <v>21.28</v>
       </c>
       <c r="H552" t="n">
         <v>23848.3</v>
@@ -56263,13 +56269,13 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H554" t="n">
         <v>37920</v>
       </c>
       <c r="I554" t="n">
-        <v>-0.4</v>
+        <v>-183.5</v>
       </c>
       <c r="J554" t="n">
         <v>38.8</v>
@@ -56360,22 +56366,22 @@
         </is>
       </c>
       <c r="D555" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="E555" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="F555" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G555" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H555" t="n">
         <v>3836.9</v>
       </c>
       <c r="I555" t="n">
-        <v>3365.1</v>
+        <v>4078.6</v>
       </c>
       <c r="J555" t="n">
         <v>61.6</v>
@@ -56478,7 +56484,7 @@
         <v>1.6</v>
       </c>
       <c r="G556" t="n">
-        <v>36.19</v>
+        <v>35.98</v>
       </c>
       <c r="H556" t="n">
         <v>46103.9</v>
@@ -56578,7 +56584,7 @@
         <v>0.7</v>
       </c>
       <c r="G557" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="H557" t="n">
         <v>4485</v>
@@ -56757,16 +56763,16 @@
         <v>0.6</v>
       </c>
       <c r="F559" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G559" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="H559" t="n">
         <v>7425</v>
       </c>
       <c r="I559" t="n">
-        <v>18.3</v>
+        <v>35.6</v>
       </c>
       <c r="J559" t="n">
         <v>48.9</v>
@@ -57027,22 +57033,22 @@
         </is>
       </c>
       <c r="D562" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="E562" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F562" t="n">
         <v>2.1</v>
       </c>
       <c r="G562" t="n">
-        <v>7.07</v>
+        <v>5.92</v>
       </c>
       <c r="H562" t="n">
         <v>1504.8</v>
       </c>
       <c r="I562" t="n">
-        <v>2671.9</v>
+        <v>2619.8</v>
       </c>
       <c r="J562" t="n">
         <v>78.5</v>
@@ -57066,10 +57072,10 @@
         <v>3.95</v>
       </c>
       <c r="Q562" t="n">
-        <v>5.8</v>
+        <v>5.58</v>
       </c>
       <c r="R562" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="S562" t="inlineStr">
         <is>
@@ -57142,7 +57148,7 @@
         <v>1.9</v>
       </c>
       <c r="G563" t="n">
-        <v>7.84</v>
+        <v>7.51</v>
       </c>
       <c r="H563" t="n">
         <v>11520</v>
@@ -57336,7 +57342,7 @@
         <v>1.2</v>
       </c>
       <c r="G565" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="H565" t="n">
         <v>9439.200000000001</v>
@@ -57433,19 +57439,19 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="E566" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G566" t="n">
-        <v>0.2</v>
+        <v>7.85</v>
       </c>
       <c r="H566" t="n">
         <v>5126.9</v>
       </c>
       <c r="I566" t="n">
-        <v>-24.1</v>
+        <v>-21.2</v>
       </c>
       <c r="J566" t="n">
         <v>23.3</v>
@@ -57618,7 +57624,7 @@
         <v>2.2</v>
       </c>
       <c r="G568" t="n">
-        <v>1.18</v>
+        <v>0.57</v>
       </c>
       <c r="H568" t="n">
         <v>6408</v>
@@ -57645,10 +57651,10 @@
         <v>24.74</v>
       </c>
       <c r="Q568" t="n">
-        <v>38.5</v>
+        <v>38.12</v>
       </c>
       <c r="R568" t="n">
-        <v>13.76</v>
+        <v>13.38</v>
       </c>
       <c r="S568" t="inlineStr">
         <is>
@@ -57808,14 +57814,8 @@
           <t>Ulaşlar Turizm Yatırımları Hisse Senedi</t>
         </is>
       </c>
-      <c r="C570" t="n">
-        <v>34.4</v>
-      </c>
       <c r="E570" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F570" t="n">
-        <v>9.1</v>
+        <v>1.6</v>
       </c>
       <c r="G570" t="n">
         <v>0.98</v>
@@ -57824,7 +57824,7 @@
         <v>753.9</v>
       </c>
       <c r="I570" t="n">
-        <v>-156.3</v>
+        <v>-97.3</v>
       </c>
       <c r="J570" t="n">
         <v>86.40000000000001</v>
@@ -58006,7 +58006,7 @@
         <v>1.1</v>
       </c>
       <c r="G572" t="n">
-        <v>9.960000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H572" t="n">
         <v>2219.4</v>
@@ -58094,7 +58094,7 @@
         <v>2.7</v>
       </c>
       <c r="G573" t="n">
-        <v>81.15000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="H573" t="n">
         <v>17688</v>
@@ -58200,7 +58200,7 @@
         <v>0.1</v>
       </c>
       <c r="G574" t="n">
-        <v>6.24</v>
+        <v>7.12</v>
       </c>
       <c r="H574" t="n">
         <v>6450</v>
@@ -58318,7 +58318,7 @@
         <v>1.5</v>
       </c>
       <c r="G576" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H576" t="n">
         <v>2377.8</v>
@@ -58424,7 +58424,7 @@
         <v>1.4</v>
       </c>
       <c r="G577" t="n">
-        <v>5.79</v>
+        <v>5.34</v>
       </c>
       <c r="H577" t="n">
         <v>4263</v>
@@ -58454,10 +58454,10 @@
         <v>1.56</v>
       </c>
       <c r="Q577" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="R577" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="S577" t="inlineStr">
         <is>
@@ -58606,7 +58606,7 @@
         <v>1.6</v>
       </c>
       <c r="G579" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H579" t="n">
         <v>12033</v>
@@ -58697,7 +58697,7 @@
         <v>1.2</v>
       </c>
       <c r="G580" t="n">
-        <v>9.75</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H580" t="n">
         <v>9150</v>
@@ -58791,7 +58791,7 @@
         <v>0.7</v>
       </c>
       <c r="G581" t="n">
-        <v>12.47</v>
+        <v>12.49</v>
       </c>
       <c r="H581" t="n">
         <v>13440</v>
@@ -58818,13 +58818,13 @@
         <v>-1.67</v>
       </c>
       <c r="P581" t="n">
-        <v>58.3574</v>
+        <v>59.5293</v>
       </c>
       <c r="Q581" t="n">
         <v>93.7</v>
       </c>
       <c r="R581" t="n">
-        <v>35.3426</v>
+        <v>34.1707</v>
       </c>
       <c r="S581" t="inlineStr">
         <is>
@@ -58888,22 +58888,22 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="E582" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="F582" t="n">
-        <v>15.7</v>
+        <v>14.2</v>
       </c>
       <c r="G582" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H582" t="n">
         <v>2250</v>
       </c>
       <c r="I582" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="J582" t="n">
         <v>91.40000000000001</v>
@@ -58924,13 +58924,13 @@
         <v>-0.91</v>
       </c>
       <c r="P582" t="n">
-        <v>51.7</v>
+        <v>54.5</v>
       </c>
       <c r="Q582" t="n">
         <v>95.5</v>
       </c>
       <c r="R582" t="n">
-        <v>43.8</v>
+        <v>41</v>
       </c>
       <c r="S582" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>1.2</v>
       </c>
       <c r="G583" t="n">
-        <v>10.76</v>
+        <v>10.77</v>
       </c>
       <c r="H583" t="n">
         <v>2503.8</v>
@@ -59029,13 +59029,13 @@
         <v>-0.45</v>
       </c>
       <c r="P583" t="n">
-        <v>18.06</v>
+        <v>18.83</v>
       </c>
       <c r="Q583" t="n">
         <v>23.58</v>
       </c>
       <c r="R583" t="n">
-        <v>5.52</v>
+        <v>4.75</v>
       </c>
       <c r="S583" t="inlineStr">
         <is>
@@ -59095,16 +59095,16 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G584" t="n">
-        <v>6.05</v>
+        <v>6.12</v>
       </c>
       <c r="H584" t="n">
         <v>2060.2</v>
       </c>
       <c r="I584" t="n">
-        <v>-4571.2</v>
+        <v>-4641.9</v>
       </c>
       <c r="J584" t="n">
         <v>36.4</v>
@@ -59149,13 +59149,13 @@
         </is>
       </c>
       <c r="V584" t="n">
-        <v>4595.8</v>
+        <v>4663</v>
       </c>
       <c r="W584" t="n">
         <v>52</v>
       </c>
       <c r="X584" t="n">
-        <v>-246.7</v>
+        <v>-394.3</v>
       </c>
       <c r="Y584" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>7.5</v>
       </c>
       <c r="G585" t="n">
-        <v>39.21</v>
+        <v>39.23</v>
       </c>
       <c r="H585" t="n">
         <v>35035</v>
@@ -59295,16 +59295,16 @@
         </is>
       </c>
       <c r="D586" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="E586" t="n">
         <v>0.3</v>
       </c>
       <c r="F586" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O586" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="P586" t="n">
         <v>6.88</v>
@@ -59331,13 +59331,13 @@
         </is>
       </c>
       <c r="V586" t="n">
-        <v>36675.1</v>
+        <v>39031.2</v>
       </c>
       <c r="W586" t="n">
         <v>1600</v>
       </c>
       <c r="X586" t="n">
-        <v>-6321.6</v>
+        <v>-1361.6</v>
       </c>
       <c r="Y586" t="inlineStr">
         <is>
@@ -59462,13 +59462,13 @@
         <v>18.2</v>
       </c>
       <c r="G588" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="H588" t="n">
         <v>1008.6</v>
       </c>
       <c r="I588" t="n">
-        <v>-52.6</v>
+        <v>-55.5</v>
       </c>
       <c r="J588" t="n">
         <v>48.3</v>
@@ -59492,10 +59492,10 @@
         <v>29.78</v>
       </c>
       <c r="Q588" t="n">
-        <v>48.32</v>
+        <v>46.7</v>
       </c>
       <c r="R588" t="n">
-        <v>18.54</v>
+        <v>16.92</v>
       </c>
       <c r="S588" t="inlineStr">
         <is>
@@ -59519,7 +59519,7 @@
         <v>30</v>
       </c>
       <c r="X588" t="n">
-        <v>-18.8</v>
+        <v>-5.7</v>
       </c>
       <c r="Y588" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>0.4</v>
       </c>
       <c r="G589" t="n">
-        <v>7.85</v>
+        <v>7.82</v>
       </c>
       <c r="H589" t="n">
         <v>9522</v>
@@ -59665,7 +59665,7 @@
         <v>4.9</v>
       </c>
       <c r="G590" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H590" t="n">
         <v>1092</v>
@@ -59695,10 +59695,10 @@
         <v>23.16</v>
       </c>
       <c r="Q590" t="n">
-        <v>34.78</v>
+        <v>34.04</v>
       </c>
       <c r="R590" t="n">
-        <v>11.62</v>
+        <v>10.88</v>
       </c>
       <c r="S590" t="inlineStr">
         <is>
@@ -59765,13 +59765,13 @@
         <v>0.4</v>
       </c>
       <c r="G591" t="n">
-        <v>9.48</v>
+        <v>9.57</v>
       </c>
       <c r="H591" t="n">
         <v>1943.4</v>
       </c>
       <c r="I591" t="n">
-        <v>312.4</v>
+        <v>424</v>
       </c>
       <c r="J591" t="n">
         <v>72.59999999999999</v>
@@ -59816,13 +59816,13 @@
         </is>
       </c>
       <c r="V591" t="n">
-        <v>4889.1</v>
+        <v>4887.7</v>
       </c>
       <c r="W591" t="n">
         <v>820</v>
       </c>
       <c r="X591" t="n">
-        <v>-431.3</v>
+        <v>-492.3</v>
       </c>
       <c r="Y591" t="inlineStr">
         <is>
@@ -59857,23 +59857,20 @@
           <t>Vişne Madencilik Hisse Senedi</t>
         </is>
       </c>
-      <c r="D592" t="n">
-        <v>38.5</v>
-      </c>
       <c r="E592" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="F592" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="G592" t="n">
-        <v>7.58</v>
+        <v>6.62</v>
       </c>
       <c r="H592" t="n">
         <v>10050.3</v>
       </c>
       <c r="I592" t="n">
-        <v>-488.1</v>
+        <v>-386.2</v>
       </c>
       <c r="J592" t="n">
         <v>20.5</v>
@@ -59918,13 +59915,13 @@
         </is>
       </c>
       <c r="V592" t="n">
-        <v>3643.9</v>
+        <v>3913.6</v>
       </c>
       <c r="W592" t="n">
         <v>117</v>
       </c>
       <c r="X592" t="n">
-        <v>64.59999999999999</v>
+        <v>-98.8</v>
       </c>
       <c r="Y592" t="inlineStr">
         <is>
@@ -59973,7 +59970,7 @@
         <v>13.3</v>
       </c>
       <c r="G593" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="H593" t="n">
         <v>4267.2</v>
@@ -60161,7 +60158,7 @@
         <v>17.7</v>
       </c>
       <c r="G595" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="H595" t="n">
         <v>1421.4</v>
@@ -60191,10 +60188,10 @@
         <v>21.2</v>
       </c>
       <c r="Q595" t="n">
-        <v>28.76</v>
+        <v>28.7</v>
       </c>
       <c r="R595" t="n">
-        <v>7.56</v>
+        <v>7.5</v>
       </c>
       <c r="S595" t="inlineStr">
         <is>
@@ -60373,7 +60370,7 @@
         <v>1.5</v>
       </c>
       <c r="G597" t="n">
-        <v>10.22</v>
+        <v>9.76</v>
       </c>
       <c r="H597" t="n">
         <v>19809</v>
@@ -60469,13 +60466,13 @@
         <v>0.8</v>
       </c>
       <c r="G598" t="n">
-        <v>0.44</v>
+        <v>0.17</v>
       </c>
       <c r="H598" t="n">
         <v>1128.8</v>
       </c>
       <c r="I598" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="J598" t="n">
         <v>91.90000000000001</v>
@@ -60520,13 +60517,13 @@
         </is>
       </c>
       <c r="V598" t="n">
-        <v>1339.7</v>
+        <v>1381.9</v>
       </c>
       <c r="W598" t="n">
         <v>645</v>
       </c>
       <c r="X598" t="n">
-        <v>-71.59999999999999</v>
+        <v>-92.40000000000001</v>
       </c>
       <c r="Y598" t="inlineStr">
         <is>
@@ -60568,7 +60565,7 @@
         <v>2.3</v>
       </c>
       <c r="G599" t="n">
-        <v>5.91</v>
+        <v>5.9</v>
       </c>
       <c r="H599" t="n">
         <v>58060.8</v>
@@ -60595,13 +60592,13 @@
         <v>-0.91</v>
       </c>
       <c r="P599" t="n">
-        <v>132.8781</v>
+        <v>133.8299</v>
       </c>
       <c r="Q599" t="n">
         <v>244</v>
       </c>
       <c r="R599" t="n">
-        <v>111.122</v>
+        <v>110.1701</v>
       </c>
       <c r="S599" t="inlineStr">
         <is>
@@ -60765,10 +60762,10 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>38.9</v>
+        <v>17.1</v>
       </c>
       <c r="D601" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="E601" t="n">
         <v>1</v>
@@ -60777,13 +60774,13 @@
         <v>0.5</v>
       </c>
       <c r="G601" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="H601" t="n">
         <v>7272.1</v>
       </c>
       <c r="I601" t="n">
-        <v>-896.4</v>
+        <v>-629.3</v>
       </c>
       <c r="J601" t="n">
         <v>29.8</v>
@@ -60828,13 +60825,13 @@
         </is>
       </c>
       <c r="V601" t="n">
-        <v>6959.2</v>
+        <v>7612.9</v>
       </c>
       <c r="W601" t="n">
         <v>300.5</v>
       </c>
       <c r="X601" t="n">
-        <v>186.7</v>
+        <v>-43.8</v>
       </c>
       <c r="Y601" t="inlineStr">
         <is>
@@ -60962,7 +60959,7 @@
         <v>1.7</v>
       </c>
       <c r="G603" t="n">
-        <v>11.81</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H603" t="n">
         <v>1630</v>
@@ -60992,10 +60989,10 @@
         <v>3.09</v>
       </c>
       <c r="Q603" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="R603" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="S603" t="inlineStr">
         <is>
@@ -61171,7 +61168,7 @@
         <v>1.2</v>
       </c>
       <c r="G605" t="n">
-        <v>6.15</v>
+        <v>5.99</v>
       </c>
       <c r="H605" t="n">
         <v>3998.4</v>
@@ -61274,7 +61271,7 @@
         <v>0.4</v>
       </c>
       <c r="G606" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H606" t="n">
         <v>2301.8</v>
@@ -61383,7 +61380,7 @@
         <v>0.8</v>
       </c>
       <c r="G607" t="n">
-        <v>8.75</v>
+        <v>8.73</v>
       </c>
       <c r="H607" t="n">
         <v>12685.1</v>
@@ -61482,7 +61479,7 @@
         <v>16.1</v>
       </c>
       <c r="G608" t="n">
-        <v>7.95</v>
+        <v>7.45</v>
       </c>
       <c r="H608" t="n">
         <v>1644.4</v>
@@ -61575,16 +61572,16 @@
         </is>
       </c>
       <c r="E609" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="G609" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="H609" t="n">
         <v>12131.9</v>
       </c>
       <c r="I609" t="n">
-        <v>19.2</v>
+        <v>715.7</v>
       </c>
       <c r="J609" t="n">
         <v>18.6</v>
@@ -61629,13 +61626,13 @@
         </is>
       </c>
       <c r="V609" t="n">
-        <v>2413.2</v>
+        <v>2839.8</v>
       </c>
       <c r="W609" t="n">
         <v>626</v>
       </c>
       <c r="X609" t="n">
-        <v>57.7</v>
+        <v>184.9</v>
       </c>
       <c r="Y609" t="inlineStr">
         <is>
@@ -61675,16 +61672,16 @@
         </is>
       </c>
       <c r="E610" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G610" t="n">
-        <v>40.72</v>
+        <v>40.81</v>
       </c>
       <c r="H610" t="n">
         <v>6352.7</v>
       </c>
       <c r="I610" t="n">
-        <v>186.2</v>
+        <v>-122.5</v>
       </c>
       <c r="J610" t="n">
         <v>24.5</v>
@@ -61726,13 +61723,13 @@
         </is>
       </c>
       <c r="V610" t="n">
-        <v>2513.8</v>
+        <v>3157.2</v>
       </c>
       <c r="W610" t="n">
-        <v>168.2</v>
+        <v>210.5</v>
       </c>
       <c r="X610" t="n">
-        <v>140.5</v>
+        <v>-28.9</v>
       </c>
       <c r="Y610" t="inlineStr">
         <is>
@@ -61781,7 +61778,7 @@
         <v>1.8</v>
       </c>
       <c r="G611" t="n">
-        <v>35.06</v>
+        <v>34.91</v>
       </c>
       <c r="H611" t="n">
         <v>15300</v>
@@ -61884,7 +61881,7 @@
         <v>1.3</v>
       </c>
       <c r="G612" t="n">
-        <v>6.88</v>
+        <v>6.84</v>
       </c>
       <c r="H612" t="n">
         <v>102696.4</v>
@@ -61914,10 +61911,10 @@
         <v>20.46</v>
       </c>
       <c r="Q612" t="n">
-        <v>23.84</v>
+        <v>23.28</v>
       </c>
       <c r="R612" t="n">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="S612" t="inlineStr">
         <is>
